--- a/research/traditional_assets/database/data/germany/germany_shoe.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_shoe.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08357235990870196</v>
+        <v>0.08335314282897585</v>
       </c>
       <c r="C2">
-        <v>8544.041245875478</v>
+        <v>8482.441914897909</v>
       </c>
       <c r="D2">
-        <v>8263.541245875478</v>
+        <v>8294.915914897909</v>
       </c>
       <c r="E2">
-        <v>-2443.9</v>
+        <v>-2350.926</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>92.974</v>
       </c>
       <c r="G2">
         <v>280.5</v>
@@ -1457,28 +1457,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.6765922</v>
       </c>
       <c r="N2">
-        <v>684.1836734693878</v>
+        <v>679.5070812693879</v>
       </c>
       <c r="O2">
-        <v>205.2551020408164</v>
+        <v>203.8521243808163</v>
       </c>
       <c r="P2">
-        <v>478.9285714285714</v>
+        <v>475.6549568885715</v>
       </c>
       <c r="Q2">
-        <v>648.9285714285714</v>
+        <v>645.6549568885715</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08357235990870196</v>
+        <v>0.08383943720098572</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896528</v>
+        <v>0.8785089422860443</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.299622504906</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08335314282897585</v>
+        <v>0.08313392574924974</v>
       </c>
       <c r="C3">
-        <v>8482.441914897909</v>
+        <v>8421.081735994601</v>
       </c>
       <c r="D3">
-        <v>8294.915914897909</v>
+        <v>8326.529735994602</v>
       </c>
       <c r="E3">
-        <v>-2350.926</v>
+        <v>-2257.952</v>
       </c>
       <c r="F3">
-        <v>92.974</v>
+        <v>185.948</v>
       </c>
       <c r="G3">
         <v>280.5</v>
@@ -1539,28 +1539,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M3">
-        <v>4.6765922</v>
+        <v>9.3531844</v>
       </c>
       <c r="N3">
-        <v>679.5070812693879</v>
+        <v>674.8304890693878</v>
       </c>
       <c r="O3">
-        <v>203.8521243808163</v>
+        <v>202.4491467208163</v>
       </c>
       <c r="P3">
-        <v>475.6549568885715</v>
+        <v>472.3813423485715</v>
       </c>
       <c r="Q3">
-        <v>645.6549568885715</v>
+        <v>642.3813423485715</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08383943720098572</v>
+        <v>0.08411196505025484</v>
       </c>
       <c r="T3">
-        <v>0.8785089422860443</v>
+        <v>0.8848028879966477</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.299622504906</v>
+        <v>73.14981125245299</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08313392574924974</v>
+        <v>0.08291470866952365</v>
       </c>
       <c r="C4">
-        <v>8421.081735994601</v>
+        <v>8359.963454016513</v>
       </c>
       <c r="D4">
-        <v>8326.529735994602</v>
+        <v>8358.385454016514</v>
       </c>
       <c r="E4">
-        <v>-2257.952</v>
+        <v>-2164.978</v>
       </c>
       <c r="F4">
-        <v>185.948</v>
+        <v>278.922</v>
       </c>
       <c r="G4">
         <v>280.5</v>
@@ -1621,28 +1621,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M4">
-        <v>9.3531844</v>
+        <v>14.0297766</v>
       </c>
       <c r="N4">
-        <v>674.8304890693878</v>
+        <v>670.1538968693878</v>
       </c>
       <c r="O4">
-        <v>202.4491467208163</v>
+        <v>201.0461690608163</v>
       </c>
       <c r="P4">
-        <v>472.3813423485715</v>
+        <v>469.1077278085715</v>
       </c>
       <c r="Q4">
-        <v>642.3813423485715</v>
+        <v>639.1077278085716</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08411196505025484</v>
+        <v>0.08439011203043675</v>
       </c>
       <c r="T4">
-        <v>0.8848028879966477</v>
+        <v>0.8912266057837586</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.14981125245299</v>
+        <v>48.76654083496867</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08291470866952365</v>
+        <v>0.08269549158979754</v>
       </c>
       <c r="C5">
-        <v>8359.963454016513</v>
+        <v>8299.089855981036</v>
       </c>
       <c r="D5">
-        <v>8358.385454016514</v>
+        <v>8390.485855981036</v>
       </c>
       <c r="E5">
-        <v>-2164.978</v>
+        <v>-2072.004</v>
       </c>
       <c r="F5">
-        <v>278.922</v>
+        <v>371.896</v>
       </c>
       <c r="G5">
         <v>280.5</v>
@@ -1703,28 +1703,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M5">
-        <v>14.0297766</v>
+        <v>18.7063688</v>
       </c>
       <c r="N5">
-        <v>670.1538968693878</v>
+        <v>665.4773046693879</v>
       </c>
       <c r="O5">
-        <v>201.0461690608163</v>
+        <v>199.6431914008164</v>
       </c>
       <c r="P5">
-        <v>469.1077278085715</v>
+        <v>465.8341132685715</v>
       </c>
       <c r="Q5">
-        <v>639.1077278085716</v>
+        <v>635.8341132685715</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08439011203043675</v>
+        <v>0.08467405373937244</v>
       </c>
       <c r="T5">
-        <v>0.8912266057837586</v>
+        <v>0.8977841510247676</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.76654083496867</v>
+        <v>36.5749056262265</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08269549158979754</v>
+        <v>0.08247627451007143</v>
       </c>
       <c r="C6">
-        <v>8299.089855981036</v>
+        <v>8238.463771884812</v>
       </c>
       <c r="D6">
-        <v>8390.485855981036</v>
+        <v>8422.833771884812</v>
       </c>
       <c r="E6">
-        <v>-2072.004</v>
+        <v>-1979.03</v>
       </c>
       <c r="F6">
-        <v>371.896</v>
+        <v>464.87</v>
       </c>
       <c r="G6">
         <v>280.5</v>
@@ -1785,28 +1785,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M6">
-        <v>18.7063688</v>
+        <v>23.382961</v>
       </c>
       <c r="N6">
-        <v>665.4773046693879</v>
+        <v>660.8007124693878</v>
       </c>
       <c r="O6">
-        <v>199.6431914008164</v>
+        <v>198.2402137408163</v>
       </c>
       <c r="P6">
-        <v>465.8341132685715</v>
+        <v>462.5604987285715</v>
       </c>
       <c r="Q6">
-        <v>635.8341132685715</v>
+        <v>632.5604987285715</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08467405373937244</v>
+        <v>0.08496397316849624</v>
       </c>
       <c r="T6">
-        <v>0.8977841510247676</v>
+        <v>0.9044797498497977</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.5749056262265</v>
+        <v>29.2599245009812</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08247627451007143</v>
+        <v>0.08225705743034532</v>
       </c>
       <c r="C7">
-        <v>8238.463771884812</v>
+        <v>8178.088075535435</v>
       </c>
       <c r="D7">
-        <v>8422.833771884812</v>
+        <v>8455.432075535435</v>
       </c>
       <c r="E7">
-        <v>-1979.03</v>
+        <v>-1886.056</v>
       </c>
       <c r="F7">
-        <v>464.87</v>
+        <v>557.8440000000001</v>
       </c>
       <c r="G7">
         <v>280.5</v>
@@ -1867,28 +1867,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M7">
-        <v>23.382961</v>
+        <v>28.0595532</v>
       </c>
       <c r="N7">
-        <v>660.8007124693878</v>
+        <v>656.1241202693878</v>
       </c>
       <c r="O7">
-        <v>198.2402137408163</v>
+        <v>196.8372360808164</v>
       </c>
       <c r="P7">
-        <v>462.5604987285715</v>
+        <v>459.2868841885715</v>
       </c>
       <c r="Q7">
-        <v>632.5604987285715</v>
+        <v>629.2868841885715</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08496397316849624</v>
+        <v>0.08526006109611205</v>
       </c>
       <c r="T7">
-        <v>0.9044797498497977</v>
+        <v>0.9113178082242968</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.2599245009812</v>
+        <v>24.38327041748433</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08225705743034532</v>
+        <v>0.08203784035061924</v>
       </c>
       <c r="C8">
-        <v>8178.088075535435</v>
+        <v>8117.965685402528</v>
       </c>
       <c r="D8">
-        <v>8455.432075535435</v>
+        <v>8488.283685402528</v>
       </c>
       <c r="E8">
-        <v>-1886.056</v>
+        <v>-1793.082</v>
       </c>
       <c r="F8">
-        <v>557.8439999999999</v>
+        <v>650.8179999999999</v>
       </c>
       <c r="G8">
         <v>280.5</v>
@@ -1949,28 +1949,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M8">
-        <v>28.0595532</v>
+        <v>32.73614539999999</v>
       </c>
       <c r="N8">
-        <v>656.1241202693878</v>
+        <v>651.4475280693879</v>
       </c>
       <c r="O8">
-        <v>196.8372360808164</v>
+        <v>195.4342584208163</v>
       </c>
       <c r="P8">
-        <v>459.2868841885715</v>
+        <v>456.0132696485715</v>
       </c>
       <c r="Q8">
-        <v>629.2868841885715</v>
+        <v>626.0132696485715</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08526006109611205</v>
+        <v>0.08556251650604219</v>
       </c>
       <c r="T8">
-        <v>0.9113178082242968</v>
+        <v>0.9183029216176023</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.38327041748434</v>
+        <v>20.89994607212943</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08203784035061923</v>
+        <v>0.08181862327089312</v>
       </c>
       <c r="C9">
-        <v>8117.96568540253</v>
+        <v>8058.099565488773</v>
       </c>
       <c r="D9">
-        <v>8488.28368540253</v>
+        <v>8521.391565488773</v>
       </c>
       <c r="E9">
-        <v>-1793.082</v>
+        <v>-1700.108</v>
       </c>
       <c r="F9">
-        <v>650.818</v>
+        <v>743.792</v>
       </c>
       <c r="G9">
         <v>280.5</v>
@@ -2031,28 +2031,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M9">
-        <v>32.7361454</v>
+        <v>37.4127376</v>
       </c>
       <c r="N9">
-        <v>651.4475280693878</v>
+        <v>646.7709358693878</v>
       </c>
       <c r="O9">
-        <v>195.4342584208163</v>
+        <v>194.0312807608163</v>
       </c>
       <c r="P9">
-        <v>456.0132696485715</v>
+        <v>452.7396551085715</v>
       </c>
       <c r="Q9">
-        <v>626.0132696485714</v>
+        <v>622.7396551085715</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08556251650604219</v>
+        <v>0.08587154703357948</v>
       </c>
       <c r="T9">
-        <v>0.9183029216176023</v>
+        <v>0.9254398853020666</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.89994607212943</v>
+        <v>18.28745281311325</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08181862327089312</v>
+        <v>0.08159940619116703</v>
       </c>
       <c r="C10">
-        <v>8058.099565488773</v>
+        <v>7998.492726221342</v>
       </c>
       <c r="D10">
-        <v>8521.391565488773</v>
+        <v>8554.758726221342</v>
       </c>
       <c r="E10">
-        <v>-1700.108</v>
+        <v>-1607.134</v>
       </c>
       <c r="F10">
-        <v>743.792</v>
+        <v>836.766</v>
       </c>
       <c r="G10">
         <v>280.5</v>
@@ -2113,28 +2113,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M10">
-        <v>37.4127376</v>
+        <v>42.08932979999999</v>
       </c>
       <c r="N10">
-        <v>646.7709358693878</v>
+        <v>642.0943436693879</v>
       </c>
       <c r="O10">
-        <v>194.0312807608163</v>
+        <v>192.6283031008163</v>
       </c>
       <c r="P10">
-        <v>452.7396551085715</v>
+        <v>449.4660405685715</v>
       </c>
       <c r="Q10">
-        <v>622.7396551085715</v>
+        <v>619.4660405685715</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08587154703357948</v>
+        <v>0.08618736944084288</v>
       </c>
       <c r="T10">
-        <v>0.9254398853020666</v>
+        <v>0.9327337053312441</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.28745281311325</v>
+        <v>16.25551361165623</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08159940619116703</v>
+        <v>0.0813801891114409</v>
       </c>
       <c r="C11">
-        <v>7998.492726221342</v>
+        <v>7939.148225364423</v>
       </c>
       <c r="D11">
-        <v>8554.758726221342</v>
+        <v>8588.388225364422</v>
       </c>
       <c r="E11">
-        <v>-1607.134</v>
+        <v>-1514.16</v>
       </c>
       <c r="F11">
-        <v>836.766</v>
+        <v>929.7399999999999</v>
       </c>
       <c r="G11">
         <v>280.5</v>
@@ -2195,28 +2195,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M11">
-        <v>42.08932979999999</v>
+        <v>46.76592199999999</v>
       </c>
       <c r="N11">
-        <v>642.0943436693879</v>
+        <v>637.4177514693879</v>
       </c>
       <c r="O11">
-        <v>192.6283031008163</v>
+        <v>191.2253254408164</v>
       </c>
       <c r="P11">
-        <v>449.4660405685715</v>
+        <v>446.1924260285715</v>
       </c>
       <c r="Q11">
-        <v>619.4660405685715</v>
+        <v>616.1924260285715</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08618736944084288</v>
+        <v>0.08651021012382323</v>
       </c>
       <c r="T11">
-        <v>0.9327337053312441</v>
+        <v>0.9401896102499591</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.25551361165623</v>
+        <v>14.6299622504906</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0813801891114409</v>
+        <v>0.0811609720317148</v>
       </c>
       <c r="C12">
-        <v>7939.148225364423</v>
+        <v>7880.069168953298</v>
       </c>
       <c r="D12">
-        <v>8588.388225364422</v>
+        <v>8622.283168953298</v>
       </c>
       <c r="E12">
-        <v>-1514.16</v>
+        <v>-1421.186</v>
       </c>
       <c r="F12">
-        <v>929.74</v>
+        <v>1022.714</v>
       </c>
       <c r="G12">
         <v>280.5</v>
@@ -2277,28 +2277,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M12">
-        <v>46.765922</v>
+        <v>51.4425142</v>
       </c>
       <c r="N12">
-        <v>637.4177514693878</v>
+        <v>632.7411592693878</v>
       </c>
       <c r="O12">
-        <v>191.2253254408163</v>
+        <v>189.8223477808163</v>
       </c>
       <c r="P12">
-        <v>446.1924260285714</v>
+        <v>442.9188114885715</v>
       </c>
       <c r="Q12">
-        <v>616.1924260285714</v>
+        <v>612.9188114885715</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08651021012382323</v>
+        <v>0.08684030565361213</v>
       </c>
       <c r="T12">
-        <v>0.9401896102499591</v>
+        <v>0.9478130635938137</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.6299622504906</v>
+        <v>13.29996568226418</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0811609720317148</v>
+        <v>0.08094175495198869</v>
       </c>
       <c r="C13">
-        <v>7880.069168953298</v>
+        <v>7821.258712250665</v>
       </c>
       <c r="D13">
-        <v>8622.283168953298</v>
+        <v>8656.446712250665</v>
       </c>
       <c r="E13">
-        <v>-1421.186</v>
+        <v>-1328.212</v>
       </c>
       <c r="F13">
-        <v>1022.714</v>
+        <v>1115.688</v>
       </c>
       <c r="G13">
         <v>280.5</v>
@@ -2359,28 +2359,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M13">
-        <v>51.4425142</v>
+        <v>56.11910639999999</v>
       </c>
       <c r="N13">
-        <v>632.7411592693878</v>
+        <v>628.0645670693879</v>
       </c>
       <c r="O13">
-        <v>189.8223477808163</v>
+        <v>188.4193701208164</v>
       </c>
       <c r="P13">
-        <v>442.9188114885715</v>
+        <v>439.6451969485715</v>
       </c>
       <c r="Q13">
-        <v>612.9188114885715</v>
+        <v>609.6451969485715</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08684030565361213</v>
+        <v>0.0871779033545326</v>
       </c>
       <c r="T13">
-        <v>0.9478130635938137</v>
+        <v>0.9556097772409379</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.29996568226418</v>
+        <v>12.19163520874217</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08094175495198869</v>
+        <v>0.08072253787226259</v>
       </c>
       <c r="C14">
-        <v>7821.258712250665</v>
+        <v>7762.720060725764</v>
       </c>
       <c r="D14">
-        <v>8656.446712250665</v>
+        <v>8690.882060725764</v>
       </c>
       <c r="E14">
-        <v>-1328.212</v>
+        <v>-1235.238</v>
       </c>
       <c r="F14">
-        <v>1115.688</v>
+        <v>1208.662</v>
       </c>
       <c r="G14">
         <v>280.5</v>
@@ -2441,28 +2441,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M14">
-        <v>56.11910639999999</v>
+        <v>60.7956986</v>
       </c>
       <c r="N14">
-        <v>628.0645670693879</v>
+        <v>623.3879748693878</v>
       </c>
       <c r="O14">
-        <v>188.4193701208164</v>
+        <v>187.0163924608163</v>
       </c>
       <c r="P14">
-        <v>439.6451969485715</v>
+        <v>436.3715824085715</v>
       </c>
       <c r="Q14">
-        <v>609.6451969485715</v>
+        <v>606.3715824085715</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0871779033545326</v>
+        <v>0.08752326192214091</v>
       </c>
       <c r="T14">
-        <v>0.9556097772409379</v>
+        <v>0.9635857256845475</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.19163520874217</v>
+        <v>11.253817115762</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08072253787226259</v>
+        <v>0.08050332079253648</v>
       </c>
       <c r="C15">
-        <v>7762.720060725764</v>
+        <v>7704.456471056987</v>
       </c>
       <c r="D15">
-        <v>8690.882060725764</v>
+        <v>8725.592471056987</v>
       </c>
       <c r="E15">
-        <v>-1235.238</v>
+        <v>-1142.264</v>
       </c>
       <c r="F15">
-        <v>1208.662</v>
+        <v>1301.636</v>
       </c>
       <c r="G15">
         <v>280.5</v>
@@ -2523,28 +2523,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M15">
-        <v>60.7956986</v>
+        <v>65.4722908</v>
       </c>
       <c r="N15">
-        <v>623.3879748693878</v>
+        <v>618.7113826693878</v>
       </c>
       <c r="O15">
-        <v>187.0163924608163</v>
+        <v>185.6134148008163</v>
       </c>
       <c r="P15">
-        <v>436.3715824085715</v>
+        <v>433.0979678685715</v>
       </c>
       <c r="Q15">
-        <v>606.3715824085715</v>
+        <v>603.0979678685715</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08752326192214091</v>
+        <v>0.08787665208434475</v>
       </c>
       <c r="T15">
-        <v>0.9635857256845475</v>
+        <v>0.9717471613012644</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.253817115762</v>
+        <v>10.44997303606471</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08050332079253648</v>
+        <v>0.08028410371281038</v>
       </c>
       <c r="C16">
-        <v>7704.456471056987</v>
+        <v>7646.471252158572</v>
       </c>
       <c r="D16">
-        <v>8725.592471056987</v>
+        <v>8760.581252158572</v>
       </c>
       <c r="E16">
-        <v>-1142.264</v>
+        <v>-1049.29</v>
       </c>
       <c r="F16">
-        <v>1301.636</v>
+        <v>1394.61</v>
       </c>
       <c r="G16">
         <v>280.5</v>
@@ -2605,28 +2605,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M16">
-        <v>65.4722908</v>
+        <v>70.148883</v>
       </c>
       <c r="N16">
-        <v>618.7113826693878</v>
+        <v>614.0347904693879</v>
       </c>
       <c r="O16">
-        <v>185.6134148008163</v>
+        <v>184.2104371408164</v>
       </c>
       <c r="P16">
-        <v>433.0979678685715</v>
+        <v>429.8243533285715</v>
       </c>
       <c r="Q16">
-        <v>603.0979678685715</v>
+        <v>599.8243533285715</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08787665208434475</v>
+        <v>0.08823835730918868</v>
       </c>
       <c r="T16">
-        <v>0.9717471613012644</v>
+        <v>0.9801006306971981</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.44997303606471</v>
+        <v>9.753308166993733</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08028410371281038</v>
+        <v>0.08006488663308427</v>
       </c>
       <c r="C17">
-        <v>7646.471252158572</v>
+        <v>7588.767766232147</v>
       </c>
       <c r="D17">
-        <v>8760.581252158572</v>
+        <v>8795.851766232146</v>
       </c>
       <c r="E17">
-        <v>-1049.29</v>
+        <v>-956.316</v>
       </c>
       <c r="F17">
-        <v>1394.61</v>
+        <v>1487.584</v>
       </c>
       <c r="G17">
         <v>280.5</v>
@@ -2687,28 +2687,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M17">
-        <v>70.148883</v>
+        <v>74.8254752</v>
       </c>
       <c r="N17">
-        <v>614.0347904693879</v>
+        <v>609.3581982693878</v>
       </c>
       <c r="O17">
-        <v>184.2104371408164</v>
+        <v>182.8074594808163</v>
       </c>
       <c r="P17">
-        <v>429.8243533285715</v>
+        <v>426.5507387885715</v>
       </c>
       <c r="Q17">
-        <v>599.8243533285715</v>
+        <v>596.5507387885715</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08823835730918868</v>
+        <v>0.08860867456319556</v>
       </c>
       <c r="T17">
-        <v>0.9801006306971981</v>
+        <v>0.9886529922216064</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.753308166993733</v>
+        <v>9.143726406556624</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08006488663308427</v>
+        <v>0.08002416955335816</v>
       </c>
       <c r="C18">
-        <v>7588.767766232147</v>
+        <v>7502.376160432387</v>
       </c>
       <c r="D18">
-        <v>8795.851766232146</v>
+        <v>8802.434160432387</v>
       </c>
       <c r="E18">
-        <v>-956.316</v>
+        <v>-863.3420000000001</v>
       </c>
       <c r="F18">
-        <v>1487.584</v>
+        <v>1580.558</v>
       </c>
       <c r="G18">
         <v>280.5</v>
@@ -2769,45 +2769,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M18">
-        <v>74.8254752</v>
+        <v>81.8729044</v>
       </c>
       <c r="N18">
-        <v>609.3581982693878</v>
+        <v>602.3107690693878</v>
       </c>
       <c r="O18">
-        <v>182.8074594808163</v>
+        <v>180.6932307208163</v>
       </c>
       <c r="P18">
-        <v>426.5507387885715</v>
+        <v>421.6175383485714</v>
       </c>
       <c r="Q18">
-        <v>596.5507387885715</v>
+        <v>591.6175383485714</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08860867456319556</v>
+        <v>0.08898791512452792</v>
       </c>
       <c r="T18">
-        <v>0.9886529922216064</v>
+        <v>0.9974114347466031</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.143726406556624</v>
+        <v>8.356655702926155</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08002416955335816</v>
+        <v>0.07981545247363205</v>
       </c>
       <c r="C19">
-        <v>7502.376160432387</v>
+        <v>7443.299009466534</v>
       </c>
       <c r="D19">
-        <v>8802.434160432387</v>
+        <v>8836.331009466534</v>
       </c>
       <c r="E19">
-        <v>-863.3420000000001</v>
+        <v>-770.3679999999999</v>
       </c>
       <c r="F19">
-        <v>1580.558</v>
+        <v>1673.532</v>
       </c>
       <c r="G19">
         <v>280.5</v>
@@ -2851,28 +2851,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M19">
-        <v>81.8729044</v>
+        <v>86.68895760000001</v>
       </c>
       <c r="N19">
-        <v>602.3107690693878</v>
+        <v>597.4947158693878</v>
       </c>
       <c r="O19">
-        <v>180.6932307208163</v>
+        <v>179.2484147608164</v>
       </c>
       <c r="P19">
-        <v>421.6175383485714</v>
+        <v>418.2463011085715</v>
       </c>
       <c r="Q19">
-        <v>591.6175383485714</v>
+        <v>588.2463011085715</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08898791512452792</v>
+        <v>0.08937640545564884</v>
       </c>
       <c r="T19">
-        <v>0.9974114347466031</v>
+        <v>1.00638349782099</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.356655702926155</v>
+        <v>7.89239705276359</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07981545247363206</v>
+        <v>0.07960673539390596</v>
       </c>
       <c r="C20">
-        <v>7443.299009466532</v>
+        <v>7384.483931029685</v>
       </c>
       <c r="D20">
-        <v>8836.331009466532</v>
+        <v>8870.489931029684</v>
       </c>
       <c r="E20">
-        <v>-770.3680000000002</v>
+        <v>-677.3940000000002</v>
       </c>
       <c r="F20">
-        <v>1673.532</v>
+        <v>1766.506</v>
       </c>
       <c r="G20">
         <v>280.5</v>
@@ -2933,28 +2933,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M20">
-        <v>86.68895759999999</v>
+        <v>91.50501079999999</v>
       </c>
       <c r="N20">
-        <v>597.4947158693878</v>
+        <v>592.6786626693878</v>
       </c>
       <c r="O20">
-        <v>179.2484147608164</v>
+        <v>177.8035988008163</v>
       </c>
       <c r="P20">
-        <v>418.2463011085715</v>
+        <v>414.8750638685715</v>
       </c>
       <c r="Q20">
-        <v>588.2463011085715</v>
+        <v>584.8750638685715</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08937640545564884</v>
+        <v>0.08977448814062464</v>
       </c>
       <c r="T20">
-        <v>1.00638349782099</v>
+        <v>1.015577093316966</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.892397052763591</v>
+        <v>7.477007734197086</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07960673539390596</v>
+        <v>0.07939801831417985</v>
       </c>
       <c r="C21">
-        <v>7384.483931029685</v>
+        <v>7325.933976226121</v>
       </c>
       <c r="D21">
-        <v>8870.489931029684</v>
+        <v>8904.91397622612</v>
       </c>
       <c r="E21">
-        <v>-677.3940000000002</v>
+        <v>-584.4200000000001</v>
       </c>
       <c r="F21">
-        <v>1766.506</v>
+        <v>1859.48</v>
       </c>
       <c r="G21">
         <v>280.5</v>
@@ -3015,28 +3015,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M21">
-        <v>91.50501079999999</v>
+        <v>96.32106399999999</v>
       </c>
       <c r="N21">
-        <v>592.6786626693878</v>
+        <v>587.8626094693878</v>
       </c>
       <c r="O21">
-        <v>177.8035988008163</v>
+        <v>176.3587828408164</v>
       </c>
       <c r="P21">
-        <v>414.8750638685715</v>
+        <v>411.5038266285715</v>
       </c>
       <c r="Q21">
-        <v>584.8750638685715</v>
+        <v>581.5038266285715</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08977448814062464</v>
+        <v>0.09018252289272481</v>
       </c>
       <c r="T21">
-        <v>1.015577093316966</v>
+        <v>1.025000528700342</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.477007734197086</v>
+        <v>7.103157347487231</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07939801831417985</v>
+        <v>0.07918930123445374</v>
       </c>
       <c r="C22">
-        <v>7325.933976226121</v>
+        <v>7267.652243706771</v>
       </c>
       <c r="D22">
-        <v>8904.91397622612</v>
+        <v>8939.60624370677</v>
       </c>
       <c r="E22">
-        <v>-584.4200000000001</v>
+        <v>-491.4459999999999</v>
       </c>
       <c r="F22">
-        <v>1859.48</v>
+        <v>1952.454</v>
       </c>
       <c r="G22">
         <v>280.5</v>
@@ -3097,28 +3097,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M22">
-        <v>96.32106399999999</v>
+        <v>101.1371172</v>
       </c>
       <c r="N22">
-        <v>587.8626094693878</v>
+        <v>583.0465562693878</v>
       </c>
       <c r="O22">
-        <v>176.3587828408164</v>
+        <v>174.9139668808163</v>
       </c>
       <c r="P22">
-        <v>411.5038266285715</v>
+        <v>408.1325893885714</v>
       </c>
       <c r="Q22">
-        <v>581.5038266285715</v>
+        <v>578.1325893885714</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09018252289272481</v>
+        <v>0.09060088763854904</v>
       </c>
       <c r="T22">
-        <v>1.025000528700342</v>
+        <v>1.034662532068107</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.103157347487231</v>
+        <v>6.764911759511648</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07918930123445374</v>
+        <v>0.07924238415472763</v>
       </c>
       <c r="C23">
-        <v>7267.652243706771</v>
+        <v>7165.829368599194</v>
       </c>
       <c r="D23">
-        <v>8939.60624370677</v>
+        <v>8930.757368599194</v>
       </c>
       <c r="E23">
-        <v>-491.4460000000001</v>
+        <v>-398.4720000000002</v>
       </c>
       <c r="F23">
-        <v>1952.454</v>
+        <v>2045.428</v>
       </c>
       <c r="G23">
         <v>280.5</v>
@@ -3179,45 +3179,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M23">
-        <v>101.1371172</v>
+        <v>109.430398</v>
       </c>
       <c r="N23">
-        <v>583.0465562693878</v>
+        <v>574.7532754693879</v>
       </c>
       <c r="O23">
-        <v>174.9139668808163</v>
+        <v>172.4259826408164</v>
       </c>
       <c r="P23">
-        <v>408.1325893885714</v>
+        <v>402.3272928285715</v>
       </c>
       <c r="Q23">
-        <v>578.1325893885714</v>
+        <v>572.3272928285714</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09060088763854904</v>
+        <v>0.09102997968554824</v>
       </c>
       <c r="T23">
-        <v>1.034662532068107</v>
+        <v>1.044572279111969</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.764911759511649</v>
+        <v>6.252226858111106</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07924238415472763</v>
+        <v>0.07904556707500153</v>
       </c>
       <c r="C24">
-        <v>7165.829368599194</v>
+        <v>7105.752859698792</v>
       </c>
       <c r="D24">
-        <v>8930.757368599194</v>
+        <v>8963.654859698792</v>
       </c>
       <c r="E24">
-        <v>-398.4720000000002</v>
+        <v>-305.498</v>
       </c>
       <c r="F24">
-        <v>2045.428</v>
+        <v>2138.402</v>
       </c>
       <c r="G24">
         <v>280.5</v>
@@ -3261,28 +3261,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M24">
-        <v>109.430398</v>
+        <v>114.404507</v>
       </c>
       <c r="N24">
-        <v>574.7532754693879</v>
+        <v>569.7791664693879</v>
       </c>
       <c r="O24">
-        <v>172.4259826408164</v>
+        <v>170.9337499408163</v>
       </c>
       <c r="P24">
-        <v>402.3272928285715</v>
+        <v>398.8454165285715</v>
       </c>
       <c r="Q24">
-        <v>572.3272928285714</v>
+        <v>568.8454165285715</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09102997968554824</v>
+        <v>0.09147021698052146</v>
       </c>
       <c r="T24">
-        <v>1.044572279111969</v>
+        <v>1.054739422182944</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.252226858111106</v>
+        <v>5.98039090775845</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07904556707500153</v>
+        <v>0.07884874999527541</v>
       </c>
       <c r="C25">
-        <v>7105.752859698792</v>
+        <v>7045.91961039914</v>
       </c>
       <c r="D25">
-        <v>8963.654859698792</v>
+        <v>8996.79561039914</v>
       </c>
       <c r="E25">
-        <v>-305.498</v>
+        <v>-212.5239999999999</v>
       </c>
       <c r="F25">
-        <v>2138.402</v>
+        <v>2231.376</v>
       </c>
       <c r="G25">
         <v>280.5</v>
@@ -3343,28 +3343,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M25">
-        <v>114.404507</v>
+        <v>119.378616</v>
       </c>
       <c r="N25">
-        <v>569.7791664693879</v>
+        <v>564.8050574693879</v>
       </c>
       <c r="O25">
-        <v>170.9337499408163</v>
+        <v>169.4415172408164</v>
       </c>
       <c r="P25">
-        <v>398.8454165285715</v>
+        <v>395.3635402285715</v>
       </c>
       <c r="Q25">
-        <v>568.8454165285715</v>
+        <v>565.3635402285715</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09147021698052146</v>
+        <v>0.09192203946746766</v>
       </c>
       <c r="T25">
-        <v>1.054739422182944</v>
+        <v>1.065174121650523</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.98039090775845</v>
+        <v>5.731207953268513</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07884874999527541</v>
+        <v>0.07879193291554931</v>
       </c>
       <c r="C26">
-        <v>7045.91961039914</v>
+        <v>6962.558301173747</v>
       </c>
       <c r="D26">
-        <v>8996.79561039914</v>
+        <v>9006.408301173748</v>
       </c>
       <c r="E26">
-        <v>-212.5240000000003</v>
+        <v>-119.5500000000002</v>
       </c>
       <c r="F26">
-        <v>2231.376</v>
+        <v>2324.35</v>
       </c>
       <c r="G26">
         <v>280.5</v>
@@ -3425,45 +3425,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M26">
-        <v>119.378616</v>
+        <v>126.212205</v>
       </c>
       <c r="N26">
-        <v>564.8050574693879</v>
+        <v>557.9714684693878</v>
       </c>
       <c r="O26">
-        <v>169.4415172408164</v>
+        <v>167.3914405408163</v>
       </c>
       <c r="P26">
-        <v>395.3635402285715</v>
+        <v>390.5800279285714</v>
       </c>
       <c r="Q26">
-        <v>565.3635402285715</v>
+        <v>560.5800279285714</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09192203946746766</v>
+        <v>0.09238591055406575</v>
       </c>
       <c r="T26">
-        <v>1.065174121650523</v>
+        <v>1.075887079770572</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.731207953268514</v>
+        <v>5.420899456351212</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07879193291554931</v>
+        <v>0.0786007158358232</v>
       </c>
       <c r="C27">
-        <v>6962.558301173747</v>
+        <v>6902.087118481231</v>
       </c>
       <c r="D27">
-        <v>9006.408301173748</v>
+        <v>9038.911118481232</v>
       </c>
       <c r="E27">
-        <v>-119.5500000000002</v>
+        <v>-26.57600000000002</v>
       </c>
       <c r="F27">
-        <v>2324.35</v>
+        <v>2417.324</v>
       </c>
       <c r="G27">
         <v>280.5</v>
@@ -3507,28 +3507,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M27">
-        <v>126.212205</v>
+        <v>131.2606932</v>
       </c>
       <c r="N27">
-        <v>557.9714684693878</v>
+        <v>552.9229802693878</v>
       </c>
       <c r="O27">
-        <v>167.3914405408163</v>
+        <v>165.8768940808164</v>
       </c>
       <c r="P27">
-        <v>390.5800279285714</v>
+        <v>387.0460861885715</v>
       </c>
       <c r="Q27">
-        <v>560.5800279285714</v>
+        <v>557.0460861885715</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09238591055406575</v>
+        <v>0.09286231869705838</v>
       </c>
       <c r="T27">
-        <v>1.075887079770572</v>
+        <v>1.08688957729927</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.420899456351212</v>
+        <v>5.212403323414627</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0786007158358232</v>
+        <v>0.0784094987560971</v>
       </c>
       <c r="C28">
-        <v>6902.087118481231</v>
+        <v>6841.851381355827</v>
       </c>
       <c r="D28">
-        <v>9038.911118481232</v>
+        <v>9071.649381355828</v>
       </c>
       <c r="E28">
-        <v>-26.57600000000002</v>
+        <v>66.39800000000014</v>
       </c>
       <c r="F28">
-        <v>2417.324</v>
+        <v>2510.298</v>
       </c>
       <c r="G28">
         <v>280.5</v>
@@ -3589,28 +3589,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M28">
-        <v>131.2606932</v>
+        <v>136.3091814</v>
       </c>
       <c r="N28">
-        <v>552.9229802693878</v>
+        <v>547.8744920693878</v>
       </c>
       <c r="O28">
-        <v>165.8768940808164</v>
+        <v>164.3623476208163</v>
       </c>
       <c r="P28">
-        <v>387.0460861885715</v>
+        <v>383.5121444485715</v>
       </c>
       <c r="Q28">
-        <v>557.0460861885715</v>
+        <v>553.5121444485715</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09286231869705838</v>
+        <v>0.09335177911794124</v>
       </c>
       <c r="T28">
-        <v>1.08688957729927</v>
+        <v>1.098193513116426</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.212403323414627</v>
+        <v>5.019351348473344</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0784094987560971</v>
+        <v>0.07821828167637099</v>
       </c>
       <c r="C29">
-        <v>6841.851381355827</v>
+        <v>6781.853657396111</v>
       </c>
       <c r="D29">
-        <v>9071.649381355828</v>
+        <v>9104.625657396111</v>
       </c>
       <c r="E29">
-        <v>66.39800000000014</v>
+        <v>159.3719999999998</v>
       </c>
       <c r="F29">
-        <v>2510.298</v>
+        <v>2603.272</v>
       </c>
       <c r="G29">
         <v>280.5</v>
@@ -3671,28 +3671,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M29">
-        <v>136.3091814</v>
+        <v>141.3576696</v>
       </c>
       <c r="N29">
-        <v>547.8744920693878</v>
+        <v>542.8260038693878</v>
       </c>
       <c r="O29">
-        <v>164.3623476208163</v>
+        <v>162.8478011608163</v>
       </c>
       <c r="P29">
-        <v>383.5121444485715</v>
+        <v>379.9782027085715</v>
       </c>
       <c r="Q29">
-        <v>553.5121444485715</v>
+        <v>549.9782027085714</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09335177911794124</v>
+        <v>0.09385483566162639</v>
       </c>
       <c r="T29">
-        <v>1.098193513116426</v>
+        <v>1.109811447150725</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.019351348473344</v>
+        <v>4.840088800313582</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07821828167637099</v>
+        <v>0.07802706459664489</v>
       </c>
       <c r="C30">
-        <v>6781.853657396111</v>
+        <v>6722.096551670686</v>
       </c>
       <c r="D30">
-        <v>9104.625657396111</v>
+        <v>9137.842551670687</v>
       </c>
       <c r="E30">
-        <v>159.3719999999998</v>
+        <v>252.346</v>
       </c>
       <c r="F30">
-        <v>2603.272</v>
+        <v>2696.246</v>
       </c>
       <c r="G30">
         <v>280.5</v>
@@ -3753,28 +3753,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M30">
-        <v>141.3576696</v>
+        <v>146.4061578</v>
       </c>
       <c r="N30">
-        <v>542.8260038693878</v>
+        <v>537.7775156693879</v>
       </c>
       <c r="O30">
-        <v>162.8478011608163</v>
+        <v>161.3332547008164</v>
       </c>
       <c r="P30">
-        <v>379.9782027085715</v>
+        <v>376.4442609685715</v>
       </c>
       <c r="Q30">
-        <v>549.9782027085714</v>
+        <v>546.4442609685715</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09385483566162639</v>
+        <v>0.09437206281217592</v>
       </c>
       <c r="T30">
-        <v>1.109811447150725</v>
+        <v>1.121756646932469</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.840088800313582</v>
+        <v>4.673189186509666</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07802706459664489</v>
+        <v>0.07783584751691879</v>
       </c>
       <c r="C31">
-        <v>6722.096551670687</v>
+        <v>6662.582707404223</v>
       </c>
       <c r="D31">
-        <v>9137.842551670687</v>
+        <v>9171.302707404222</v>
       </c>
       <c r="E31">
-        <v>252.3459999999995</v>
+        <v>345.3199999999997</v>
       </c>
       <c r="F31">
-        <v>2696.246</v>
+        <v>2789.22</v>
       </c>
       <c r="G31">
         <v>280.5</v>
@@ -3835,28 +3835,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M31">
-        <v>146.4061578</v>
+        <v>151.454646</v>
       </c>
       <c r="N31">
-        <v>537.7775156693879</v>
+        <v>532.7290274693878</v>
       </c>
       <c r="O31">
-        <v>161.3332547008164</v>
+        <v>159.8187082408163</v>
       </c>
       <c r="P31">
-        <v>376.4442609685715</v>
+        <v>372.9103192285714</v>
       </c>
       <c r="Q31">
-        <v>546.4442609685715</v>
+        <v>542.9103192285714</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09437206281217592</v>
+        <v>0.09490406788131256</v>
       </c>
       <c r="T31">
-        <v>1.121756646932469</v>
+        <v>1.134043138136549</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.673189186509667</v>
+        <v>4.51741621362601</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07783584751691879</v>
+        <v>0.07764463043719266</v>
       </c>
       <c r="C32">
-        <v>6662.582707404223</v>
+        <v>6603.314806678578</v>
       </c>
       <c r="D32">
-        <v>9171.302707404222</v>
+        <v>9205.008806678577</v>
       </c>
       <c r="E32">
-        <v>345.3199999999997</v>
+        <v>438.2939999999999</v>
       </c>
       <c r="F32">
-        <v>2789.22</v>
+        <v>2882.194</v>
       </c>
       <c r="G32">
         <v>280.5</v>
@@ -3917,28 +3917,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M32">
-        <v>151.454646</v>
+        <v>156.5031342</v>
       </c>
       <c r="N32">
-        <v>532.7290274693878</v>
+        <v>527.6805392693879</v>
       </c>
       <c r="O32">
-        <v>159.8187082408163</v>
+        <v>158.3041617808163</v>
       </c>
       <c r="P32">
-        <v>372.9103192285714</v>
+        <v>369.3763774885715</v>
       </c>
       <c r="Q32">
-        <v>542.9103192285714</v>
+        <v>539.3763774885715</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09490406788131256</v>
+        <v>0.09545149338723577</v>
       </c>
       <c r="T32">
-        <v>1.134043138136549</v>
+        <v>1.146685759520456</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.51741621362601</v>
+        <v>4.371693109960656</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07764463043719266</v>
+        <v>0.07767741335746657</v>
       </c>
       <c r="C33">
-        <v>6603.314806678578</v>
+        <v>6504.54453042083</v>
       </c>
       <c r="D33">
-        <v>9205.008806678577</v>
+        <v>9199.212530420829</v>
       </c>
       <c r="E33">
-        <v>438.2939999999999</v>
+        <v>531.268</v>
       </c>
       <c r="F33">
-        <v>2882.194</v>
+        <v>2975.168</v>
       </c>
       <c r="G33">
         <v>280.5</v>
@@ -3999,45 +3999,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M33">
-        <v>156.5031342</v>
+        <v>164.5267904</v>
       </c>
       <c r="N33">
-        <v>527.6805392693879</v>
+        <v>519.6568830693878</v>
       </c>
       <c r="O33">
-        <v>158.3041617808163</v>
+        <v>155.8970649208163</v>
       </c>
       <c r="P33">
-        <v>369.3763774885715</v>
+        <v>363.7598181485715</v>
       </c>
       <c r="Q33">
-        <v>539.3763774885715</v>
+        <v>533.7598181485715</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09545149338723577</v>
+        <v>0.0960150196433332</v>
       </c>
       <c r="T33">
-        <v>1.146685759520456</v>
+        <v>1.159700222709774</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.371693109960656</v>
+        <v>4.158494016725119</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07767741335746657</v>
+        <v>0.07749319627774047</v>
       </c>
       <c r="C34">
-        <v>6504.54453042083</v>
+        <v>6444.236624601999</v>
       </c>
       <c r="D34">
-        <v>9199.212530420829</v>
+        <v>9231.878624601999</v>
       </c>
       <c r="E34">
-        <v>531.268</v>
+        <v>624.2419999999997</v>
       </c>
       <c r="F34">
-        <v>2975.168</v>
+        <v>3068.142</v>
       </c>
       <c r="G34">
         <v>280.5</v>
@@ -4081,28 +4081,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M34">
-        <v>164.5267904</v>
+        <v>169.6682526</v>
       </c>
       <c r="N34">
-        <v>519.6568830693878</v>
+        <v>514.5154208693879</v>
       </c>
       <c r="O34">
-        <v>155.8970649208163</v>
+        <v>154.3546262608164</v>
       </c>
       <c r="P34">
-        <v>363.7598181485715</v>
+        <v>360.1607946085715</v>
       </c>
       <c r="Q34">
-        <v>533.7598181485715</v>
+        <v>530.1607946085715</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0960150196433332</v>
+        <v>0.09659536757871712</v>
       </c>
       <c r="T34">
-        <v>1.159700222709774</v>
+        <v>1.173103177337578</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.158494016725119</v>
+        <v>4.032479046521328</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07749319627774047</v>
+        <v>0.07730897919801435</v>
       </c>
       <c r="C35">
-        <v>6444.236624601999</v>
+        <v>6384.161537918813</v>
       </c>
       <c r="D35">
-        <v>9231.878624601999</v>
+        <v>9264.777537918813</v>
       </c>
       <c r="E35">
-        <v>624.2419999999997</v>
+        <v>717.2159999999999</v>
       </c>
       <c r="F35">
-        <v>3068.142</v>
+        <v>3161.116</v>
       </c>
       <c r="G35">
         <v>280.5</v>
@@ -4163,28 +4163,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M35">
-        <v>169.6682526</v>
+        <v>174.8097148</v>
       </c>
       <c r="N35">
-        <v>514.5154208693879</v>
+        <v>509.3739586693878</v>
       </c>
       <c r="O35">
-        <v>154.3546262608164</v>
+        <v>152.8121876008163</v>
       </c>
       <c r="P35">
-        <v>360.1607946085715</v>
+        <v>356.5617710685715</v>
       </c>
       <c r="Q35">
-        <v>530.1607946085715</v>
+        <v>526.5617710685715</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09659536757871712</v>
+        <v>0.09719330181517327</v>
       </c>
       <c r="T35">
-        <v>1.173103177337578</v>
+        <v>1.186912282105618</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.032479046521328</v>
+        <v>3.913876721623642</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07730897919801435</v>
+        <v>0.07712476211828825</v>
       </c>
       <c r="C36">
-        <v>6384.161537918813</v>
+        <v>6324.321768310212</v>
       </c>
       <c r="D36">
-        <v>9264.777537918813</v>
+        <v>9297.911768310212</v>
       </c>
       <c r="E36">
-        <v>717.2159999999999</v>
+        <v>810.1900000000001</v>
       </c>
       <c r="F36">
-        <v>3161.116</v>
+        <v>3254.09</v>
       </c>
       <c r="G36">
         <v>280.5</v>
@@ -4245,28 +4245,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M36">
-        <v>174.8097148</v>
+        <v>179.951177</v>
       </c>
       <c r="N36">
-        <v>509.3739586693878</v>
+        <v>504.2324964693878</v>
       </c>
       <c r="O36">
-        <v>152.8121876008163</v>
+        <v>151.2697489408163</v>
       </c>
       <c r="P36">
-        <v>356.5617710685715</v>
+        <v>352.9627475285715</v>
       </c>
       <c r="Q36">
-        <v>526.5617710685715</v>
+        <v>522.9627475285715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09719330181517327</v>
+        <v>0.09780963402813578</v>
       </c>
       <c r="T36">
-        <v>1.186912282105618</v>
+        <v>1.201146282404983</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.913876721623642</v>
+        <v>3.802051672434395</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07712476211828825</v>
+        <v>0.07694054503856215</v>
       </c>
       <c r="C37">
-        <v>6324.321768310212</v>
+        <v>6264.719849577574</v>
       </c>
       <c r="D37">
-        <v>9297.911768310212</v>
+        <v>9331.283849577574</v>
       </c>
       <c r="E37">
-        <v>810.1900000000001</v>
+        <v>903.1640000000002</v>
       </c>
       <c r="F37">
-        <v>3254.09</v>
+        <v>3347.064</v>
       </c>
       <c r="G37">
         <v>280.5</v>
@@ -4327,28 +4327,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M37">
-        <v>179.951177</v>
+        <v>185.0926392</v>
       </c>
       <c r="N37">
-        <v>504.2324964693878</v>
+        <v>499.0910342693878</v>
       </c>
       <c r="O37">
-        <v>151.2697489408163</v>
+        <v>149.7273102808163</v>
       </c>
       <c r="P37">
-        <v>352.9627475285715</v>
+        <v>349.3637239885715</v>
       </c>
       <c r="Q37">
-        <v>522.9627475285715</v>
+        <v>519.3637239885715</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09780963402813578</v>
+        <v>0.09844522662275336</v>
       </c>
       <c r="T37">
-        <v>1.201146282404983</v>
+        <v>1.215825095213704</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.802051672434395</v>
+        <v>3.696439125977883</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07694054503856215</v>
+        <v>0.07675632795883605</v>
       </c>
       <c r="C38">
-        <v>6264.719849577574</v>
+        <v>6205.358352030602</v>
       </c>
       <c r="D38">
-        <v>9331.283849577574</v>
+        <v>9364.896352030602</v>
       </c>
       <c r="E38">
-        <v>903.1639999999998</v>
+        <v>996.1379999999999</v>
       </c>
       <c r="F38">
-        <v>3347.064</v>
+        <v>3440.038</v>
       </c>
       <c r="G38">
         <v>280.5</v>
@@ -4409,28 +4409,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M38">
-        <v>185.0926392</v>
+        <v>190.2341014</v>
       </c>
       <c r="N38">
-        <v>499.0910342693878</v>
+        <v>493.9495720693878</v>
       </c>
       <c r="O38">
-        <v>149.7273102808163</v>
+        <v>148.1848716208164</v>
       </c>
       <c r="P38">
-        <v>349.3637239885715</v>
+        <v>345.7647004485715</v>
       </c>
       <c r="Q38">
-        <v>519.3637239885715</v>
+        <v>515.7647004485715</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09844522662275336</v>
+        <v>0.09910099676005721</v>
       </c>
       <c r="T38">
-        <v>1.215825095213704</v>
+        <v>1.230969902079843</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.696439125977884</v>
+        <v>3.596535365816319</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07675632795883605</v>
+        <v>0.07657211087910994</v>
       </c>
       <c r="C39">
-        <v>6205.358352030602</v>
+        <v>6146.239883147259</v>
       </c>
       <c r="D39">
-        <v>9364.896352030602</v>
+        <v>9398.751883147259</v>
       </c>
       <c r="E39">
-        <v>996.1379999999999</v>
+        <v>1089.112</v>
       </c>
       <c r="F39">
-        <v>3440.038</v>
+        <v>3533.012</v>
       </c>
       <c r="G39">
         <v>280.5</v>
@@ -4491,28 +4491,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M39">
-        <v>190.2341014</v>
+        <v>195.3755636</v>
       </c>
       <c r="N39">
-        <v>493.9495720693878</v>
+        <v>488.8081098693879</v>
       </c>
       <c r="O39">
-        <v>148.1848716208164</v>
+        <v>146.6424329608164</v>
       </c>
       <c r="P39">
-        <v>345.7647004485715</v>
+        <v>342.1656769085715</v>
       </c>
       <c r="Q39">
-        <v>515.7647004485715</v>
+        <v>512.1656769085715</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09910099676005721</v>
+        <v>0.09977792077275796</v>
       </c>
       <c r="T39">
-        <v>1.230969902079843</v>
+        <v>1.246603251102955</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.596535365816319</v>
+        <v>3.501889698294838</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07657211087910994</v>
+        <v>0.07638789379938382</v>
       </c>
       <c r="C40">
-        <v>6146.239883147259</v>
+        <v>6087.367088248028</v>
       </c>
       <c r="D40">
-        <v>9398.751883147259</v>
+        <v>9432.853088248028</v>
       </c>
       <c r="E40">
-        <v>1089.112</v>
+        <v>1182.086</v>
       </c>
       <c r="F40">
-        <v>3533.012</v>
+        <v>3625.986</v>
       </c>
       <c r="G40">
         <v>280.5</v>
@@ -4573,28 +4573,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M40">
-        <v>195.3755636</v>
+        <v>200.5170258</v>
       </c>
       <c r="N40">
-        <v>488.8081098693879</v>
+        <v>483.6666476693878</v>
       </c>
       <c r="O40">
-        <v>146.6424329608164</v>
+        <v>145.0999943008163</v>
       </c>
       <c r="P40">
-        <v>342.1656769085715</v>
+        <v>338.5666533685715</v>
       </c>
       <c r="Q40">
-        <v>512.1656769085715</v>
+        <v>508.5666533685715</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09977792077275796</v>
+        <v>0.1004770390153833</v>
       </c>
       <c r="T40">
-        <v>1.246603251102955</v>
+        <v>1.262749168946497</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.501889698294838</v>
+        <v>3.412097654748816</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07638789379938382</v>
+        <v>0.07620367671965772</v>
       </c>
       <c r="C41">
-        <v>6087.367088248028</v>
+        <v>6028.742651184936</v>
       </c>
       <c r="D41">
-        <v>9432.853088248028</v>
+        <v>9467.202651184936</v>
       </c>
       <c r="E41">
-        <v>1182.086</v>
+        <v>1275.06</v>
       </c>
       <c r="F41">
-        <v>3625.986</v>
+        <v>3718.96</v>
       </c>
       <c r="G41">
         <v>280.5</v>
@@ -4655,28 +4655,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M41">
-        <v>200.5170258</v>
+        <v>205.658488</v>
       </c>
       <c r="N41">
-        <v>483.6666476693878</v>
+        <v>478.5251854693878</v>
       </c>
       <c r="O41">
-        <v>145.0999943008163</v>
+        <v>143.5575556408163</v>
       </c>
       <c r="P41">
-        <v>338.5666533685715</v>
+        <v>334.9676298285715</v>
       </c>
       <c r="Q41">
-        <v>508.5666533685715</v>
+        <v>504.9676298285715</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1004770390153833</v>
+        <v>0.1011994611994295</v>
       </c>
       <c r="T41">
-        <v>1.262749168946497</v>
+        <v>1.279433284051491</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.412097654748816</v>
+        <v>3.326795213380096</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07620367671965772</v>
+        <v>0.07601945963993162</v>
       </c>
       <c r="C42">
-        <v>6028.742651184936</v>
+        <v>5970.369295045693</v>
       </c>
       <c r="D42">
-        <v>9467.202651184936</v>
+        <v>9501.803295045693</v>
       </c>
       <c r="E42">
-        <v>1275.06</v>
+        <v>1368.034</v>
       </c>
       <c r="F42">
-        <v>3718.96</v>
+        <v>3811.934</v>
       </c>
       <c r="G42">
         <v>280.5</v>
@@ -4737,28 +4737,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M42">
-        <v>205.658488</v>
+        <v>210.7999502</v>
       </c>
       <c r="N42">
-        <v>478.5251854693878</v>
+        <v>473.3837232693878</v>
       </c>
       <c r="O42">
-        <v>143.5575556408163</v>
+        <v>142.0151169808163</v>
       </c>
       <c r="P42">
-        <v>334.9676298285715</v>
+        <v>331.3686062885715</v>
       </c>
       <c r="Q42">
-        <v>504.9676298285715</v>
+        <v>501.3686062885715</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1011994611994295</v>
+        <v>0.1019463722710705</v>
       </c>
       <c r="T42">
-        <v>1.279433284051491</v>
+        <v>1.296682962380382</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.326795213380096</v>
+        <v>3.245653866712288</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07601945963993162</v>
+        <v>0.07583524256020552</v>
       </c>
       <c r="C43">
-        <v>5970.369295045693</v>
+        <v>5912.249782873289</v>
       </c>
       <c r="D43">
-        <v>9501.803295045693</v>
+        <v>9536.65778287329</v>
       </c>
       <c r="E43">
-        <v>1368.034</v>
+        <v>1461.008</v>
       </c>
       <c r="F43">
-        <v>3811.934</v>
+        <v>3904.908</v>
       </c>
       <c r="G43">
         <v>280.5</v>
@@ -4819,28 +4819,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M43">
-        <v>210.7999502</v>
+        <v>215.9414124</v>
       </c>
       <c r="N43">
-        <v>473.3837232693878</v>
+        <v>468.2422610693878</v>
       </c>
       <c r="O43">
-        <v>142.0151169808163</v>
+        <v>140.4726783208164</v>
       </c>
       <c r="P43">
-        <v>331.3686062885715</v>
+        <v>327.7695827485715</v>
       </c>
       <c r="Q43">
-        <v>501.3686062885715</v>
+        <v>497.7695827485715</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1019463722710705</v>
+        <v>0.1027190388969061</v>
       </c>
       <c r="T43">
-        <v>1.296682962380382</v>
+        <v>1.314527457203373</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.245653866712288</v>
+        <v>3.168376393695329</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07583524256020552</v>
+        <v>0.07565102548047942</v>
       </c>
       <c r="C44">
-        <v>5912.24978287329</v>
+        <v>5854.386918401526</v>
       </c>
       <c r="D44">
-        <v>9536.65778287329</v>
+        <v>9571.768918401525</v>
       </c>
       <c r="E44">
-        <v>1461.008</v>
+        <v>1553.982</v>
       </c>
       <c r="F44">
-        <v>3904.908</v>
+        <v>3997.882</v>
       </c>
       <c r="G44">
         <v>280.5</v>
@@ -4901,28 +4901,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M44">
-        <v>215.9414124</v>
+        <v>221.0828746</v>
       </c>
       <c r="N44">
-        <v>468.2422610693878</v>
+        <v>463.1007988693879</v>
       </c>
       <c r="O44">
-        <v>140.4726783208164</v>
+        <v>138.9302396608163</v>
       </c>
       <c r="P44">
-        <v>327.7695827485715</v>
+        <v>324.1705592085715</v>
       </c>
       <c r="Q44">
-        <v>497.7695827485715</v>
+        <v>494.1705592085715</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1027190388969061</v>
+        <v>0.10351881663242</v>
       </c>
       <c r="T44">
-        <v>1.314527457203373</v>
+        <v>1.332998074651732</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.168376393695329</v>
+        <v>3.094693221748926</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07565102548047942</v>
+        <v>0.0754668084007533</v>
       </c>
       <c r="C45">
-        <v>5854.386918401526</v>
+        <v>5796.783546806837</v>
       </c>
       <c r="D45">
-        <v>9571.768918401525</v>
+        <v>9607.139546806837</v>
       </c>
       <c r="E45">
-        <v>1553.982</v>
+        <v>1646.956</v>
       </c>
       <c r="F45">
-        <v>3997.882</v>
+        <v>4090.856</v>
       </c>
       <c r="G45">
         <v>280.5</v>
@@ -4983,28 +4983,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M45">
-        <v>221.0828746</v>
+        <v>226.2243368</v>
       </c>
       <c r="N45">
-        <v>463.1007988693879</v>
+        <v>457.9593366693878</v>
       </c>
       <c r="O45">
-        <v>138.9302396608163</v>
+        <v>137.3878010008164</v>
       </c>
       <c r="P45">
-        <v>324.1705592085715</v>
+        <v>320.5715356685715</v>
       </c>
       <c r="Q45">
-        <v>494.1705592085715</v>
+        <v>490.5715356685715</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.10351881663242</v>
+        <v>0.104347157858488</v>
       </c>
       <c r="T45">
-        <v>1.332998074651732</v>
+        <v>1.352128357008962</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.094693221748926</v>
+        <v>3.024359284890996</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0754668084007533</v>
+        <v>0.07607009132102721</v>
       </c>
       <c r="C46">
-        <v>5796.783546806837</v>
+        <v>5588.938201431625</v>
       </c>
       <c r="D46">
-        <v>9607.139546806837</v>
+        <v>9492.268201431625</v>
       </c>
       <c r="E46">
-        <v>1646.956</v>
+        <v>1739.93</v>
       </c>
       <c r="F46">
-        <v>4090.856</v>
+        <v>4183.83</v>
       </c>
       <c r="G46">
         <v>280.5</v>
@@ -5065,45 +5065,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M46">
-        <v>226.2243368</v>
+        <v>241.825374</v>
       </c>
       <c r="N46">
-        <v>457.9593366693878</v>
+        <v>442.3582994693878</v>
       </c>
       <c r="O46">
-        <v>137.3878010008164</v>
+        <v>132.7074898408164</v>
       </c>
       <c r="P46">
-        <v>320.5715356685715</v>
+        <v>309.6508096285714</v>
       </c>
       <c r="Q46">
-        <v>490.5715356685715</v>
+        <v>479.6508096285714</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.104347157858488</v>
+        <v>0.1052056205836858</v>
       </c>
       <c r="T46">
-        <v>1.352128357008962</v>
+        <v>1.371954285997363</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.024359284890996</v>
+        <v>2.82924683275539</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07607009132102721</v>
+        <v>0.0759033742413011</v>
       </c>
       <c r="C47">
-        <v>5588.938201431625</v>
+        <v>5527.433283834531</v>
       </c>
       <c r="D47">
-        <v>9492.268201431625</v>
+        <v>9523.737283834531</v>
       </c>
       <c r="E47">
-        <v>1739.93</v>
+        <v>1832.904</v>
       </c>
       <c r="F47">
-        <v>4183.83</v>
+        <v>4276.804</v>
       </c>
       <c r="G47">
         <v>280.5</v>
@@ -5147,28 +5147,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M47">
-        <v>241.825374</v>
+        <v>247.1992712</v>
       </c>
       <c r="N47">
-        <v>442.3582994693878</v>
+        <v>436.9844022693878</v>
       </c>
       <c r="O47">
-        <v>132.7074898408164</v>
+        <v>131.0953206808163</v>
       </c>
       <c r="P47">
-        <v>309.6508096285714</v>
+        <v>305.8890815885715</v>
       </c>
       <c r="Q47">
-        <v>479.6508096285714</v>
+        <v>475.8890815885715</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1052056205836858</v>
+        <v>0.1060958782246317</v>
       </c>
       <c r="T47">
-        <v>1.371954285997363</v>
+        <v>1.392514508652001</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.82924683275539</v>
+        <v>2.767741466825925</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0759033742413011</v>
+        <v>0.07573665716157499</v>
       </c>
       <c r="C48">
-        <v>5527.433283834531</v>
+        <v>5466.137714968943</v>
       </c>
       <c r="D48">
-        <v>9523.737283834531</v>
+        <v>9555.415714968944</v>
       </c>
       <c r="E48">
-        <v>1832.904</v>
+        <v>1925.878</v>
       </c>
       <c r="F48">
-        <v>4276.804</v>
+        <v>4369.778</v>
       </c>
       <c r="G48">
         <v>280.5</v>
@@ -5229,28 +5229,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M48">
-        <v>247.1992712</v>
+        <v>252.5731684</v>
       </c>
       <c r="N48">
-        <v>436.9844022693878</v>
+        <v>431.6105050693878</v>
       </c>
       <c r="O48">
-        <v>131.0953206808163</v>
+        <v>129.4831515208163</v>
       </c>
       <c r="P48">
-        <v>305.8890815885715</v>
+        <v>302.1273535485715</v>
       </c>
       <c r="Q48">
-        <v>475.8890815885715</v>
+        <v>472.1273535485715</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1060958782246317</v>
+        <v>0.1070197304935377</v>
       </c>
       <c r="T48">
-        <v>1.392514508652001</v>
+        <v>1.413850588765305</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.767741466825925</v>
+        <v>2.70885335051048</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07573665716157499</v>
+        <v>0.07556994008184889</v>
       </c>
       <c r="C49">
-        <v>5466.137714968943</v>
+        <v>5405.053590852</v>
       </c>
       <c r="D49">
-        <v>9555.415714968944</v>
+        <v>9587.305590852</v>
       </c>
       <c r="E49">
-        <v>1925.878</v>
+        <v>2018.852</v>
       </c>
       <c r="F49">
-        <v>4369.778</v>
+        <v>4462.752</v>
       </c>
       <c r="G49">
         <v>280.5</v>
@@ -5311,28 +5311,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M49">
-        <v>252.5731684</v>
+        <v>257.9470656</v>
       </c>
       <c r="N49">
-        <v>431.6105050693878</v>
+        <v>426.2366078693878</v>
       </c>
       <c r="O49">
-        <v>129.4831515208163</v>
+        <v>127.8709823608163</v>
       </c>
       <c r="P49">
-        <v>302.1273535485715</v>
+        <v>298.3656255085715</v>
       </c>
       <c r="Q49">
-        <v>472.1273535485715</v>
+        <v>468.3656255085715</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1070197304935377</v>
+        <v>0.1079791155420171</v>
       </c>
       <c r="T49">
-        <v>1.413850588765305</v>
+        <v>1.436007287344505</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.70885335051048</v>
+        <v>2.652418905708179</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07556994008184889</v>
+        <v>0.07540322300212277</v>
       </c>
       <c r="C50">
-        <v>5405.053590852001</v>
+        <v>5344.183035575222</v>
       </c>
       <c r="D50">
-        <v>9587.305590852</v>
+        <v>9619.409035575221</v>
       </c>
       <c r="E50">
-        <v>2018.851999999999</v>
+        <v>2111.826</v>
       </c>
       <c r="F50">
-        <v>4462.751999999999</v>
+        <v>4555.726</v>
       </c>
       <c r="G50">
         <v>280.5</v>
@@ -5393,28 +5393,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M50">
-        <v>257.9470656</v>
+        <v>263.3209628</v>
       </c>
       <c r="N50">
-        <v>426.2366078693879</v>
+        <v>420.8627106693878</v>
       </c>
       <c r="O50">
-        <v>127.8709823608164</v>
+        <v>126.2588132008163</v>
       </c>
       <c r="P50">
-        <v>298.3656255085715</v>
+        <v>294.6038974685715</v>
       </c>
       <c r="Q50">
-        <v>468.3656255085715</v>
+        <v>464.6038974685715</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1079791155420171</v>
+        <v>0.1089761235335741</v>
       </c>
       <c r="T50">
-        <v>1.436007287344505</v>
+        <v>1.459032876064066</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.652418905708179</v>
+        <v>2.598287907632502</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07540322300212277</v>
+        <v>0.07523650592239667</v>
       </c>
       <c r="C51">
-        <v>5344.183035575222</v>
+        <v>5283.528201776085</v>
       </c>
       <c r="D51">
-        <v>9619.409035575221</v>
+        <v>9651.728201776084</v>
       </c>
       <c r="E51">
-        <v>2111.826</v>
+        <v>2204.8</v>
       </c>
       <c r="F51">
-        <v>4555.726</v>
+        <v>4648.7</v>
       </c>
       <c r="G51">
         <v>280.5</v>
@@ -5475,28 +5475,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M51">
-        <v>263.3209628</v>
+        <v>268.69486</v>
       </c>
       <c r="N51">
-        <v>420.8627106693878</v>
+        <v>415.4888134693878</v>
       </c>
       <c r="O51">
-        <v>126.2588132008163</v>
+        <v>124.6466440408163</v>
       </c>
       <c r="P51">
-        <v>294.6038974685715</v>
+        <v>290.8421694285715</v>
       </c>
       <c r="Q51">
-        <v>464.6038974685715</v>
+        <v>460.8421694285715</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1089761235335741</v>
+        <v>0.1100130118447933</v>
       </c>
       <c r="T51">
-        <v>1.459032876064066</v>
+        <v>1.48297948833241</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.598287907632502</v>
+        <v>2.546322149479852</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07523650592239667</v>
+        <v>0.07631928884267056</v>
       </c>
       <c r="C52">
-        <v>5283.528201776085</v>
+        <v>4984.442166639069</v>
       </c>
       <c r="D52">
-        <v>9651.728201776084</v>
+        <v>9445.616166639069</v>
       </c>
       <c r="E52">
-        <v>2204.8</v>
+        <v>2297.774</v>
       </c>
       <c r="F52">
-        <v>4648.7</v>
+        <v>4741.674</v>
       </c>
       <c r="G52">
         <v>280.5</v>
@@ -5557,45 +5557,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M52">
-        <v>268.69486</v>
+        <v>290.6646162</v>
       </c>
       <c r="N52">
-        <v>415.4888134693878</v>
+        <v>393.5190572693878</v>
       </c>
       <c r="O52">
-        <v>124.6466440408163</v>
+        <v>118.0557171808163</v>
       </c>
       <c r="P52">
-        <v>290.8421694285715</v>
+        <v>275.4633400885715</v>
       </c>
       <c r="Q52">
-        <v>460.8421694285715</v>
+        <v>445.4633400885715</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1100130118447933</v>
+        <v>0.1110922221278991</v>
       </c>
       <c r="T52">
-        <v>1.48297948833241</v>
+        <v>1.5079035133464</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.546322149479852</v>
+        <v>2.353859518279362</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07631928884267056</v>
+        <v>0.07617707176294446</v>
       </c>
       <c r="C53">
-        <v>4984.442166639069</v>
+        <v>4918.036160436685</v>
       </c>
       <c r="D53">
-        <v>9445.616166639069</v>
+        <v>9472.184160436685</v>
       </c>
       <c r="E53">
-        <v>2297.774</v>
+        <v>2390.748</v>
       </c>
       <c r="F53">
-        <v>4741.674</v>
+        <v>4834.648</v>
       </c>
       <c r="G53">
         <v>280.5</v>
@@ -5639,28 +5639,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M53">
-        <v>290.6646162</v>
+        <v>296.3639224</v>
       </c>
       <c r="N53">
-        <v>393.5190572693878</v>
+        <v>387.8197510693878</v>
       </c>
       <c r="O53">
-        <v>118.0557171808163</v>
+        <v>116.3459253208163</v>
       </c>
       <c r="P53">
-        <v>275.4633400885715</v>
+        <v>271.4738257485715</v>
       </c>
       <c r="Q53">
-        <v>445.4633400885715</v>
+        <v>441.4738257485715</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1110922221278991</v>
+        <v>0.1122163995061343</v>
       </c>
       <c r="T53">
-        <v>1.5079035133464</v>
+        <v>1.53386603940264</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.353859518279362</v>
+        <v>2.308592989081682</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07617707176294446</v>
+        <v>0.07603485468321836</v>
       </c>
       <c r="C54">
-        <v>4918.036160436685</v>
+        <v>4851.780033135331</v>
       </c>
       <c r="D54">
-        <v>9472.184160436685</v>
+        <v>9498.902033135331</v>
       </c>
       <c r="E54">
-        <v>2390.748</v>
+        <v>2483.722</v>
       </c>
       <c r="F54">
-        <v>4834.648</v>
+        <v>4927.622</v>
       </c>
       <c r="G54">
         <v>280.5</v>
@@ -5721,28 +5721,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M54">
-        <v>296.3639224</v>
+        <v>302.0632286</v>
       </c>
       <c r="N54">
-        <v>387.8197510693878</v>
+        <v>382.1204448693878</v>
       </c>
       <c r="O54">
-        <v>116.3459253208163</v>
+        <v>114.6361334608163</v>
       </c>
       <c r="P54">
-        <v>271.4738257485715</v>
+        <v>267.4843114085715</v>
       </c>
       <c r="Q54">
-        <v>441.4738257485715</v>
+        <v>437.4843114085715</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1122163995061343</v>
+        <v>0.1133884142196135</v>
       </c>
       <c r="T54">
-        <v>1.53386603940264</v>
+        <v>1.560933353801698</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.308592989081682</v>
+        <v>2.265034630797123</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07603485468321836</v>
+        <v>0.07695103760349224</v>
       </c>
       <c r="C55">
-        <v>4851.780033135331</v>
+        <v>4589.280623090325</v>
       </c>
       <c r="D55">
-        <v>9498.902033135331</v>
+        <v>9329.376623090326</v>
       </c>
       <c r="E55">
-        <v>2483.722</v>
+        <v>2576.696</v>
       </c>
       <c r="F55">
-        <v>4927.622</v>
+        <v>5020.596</v>
       </c>
       <c r="G55">
         <v>280.5</v>
@@ -5803,45 +5803,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M55">
-        <v>302.0632286</v>
+        <v>321.8202036000001</v>
       </c>
       <c r="N55">
-        <v>382.1204448693878</v>
+        <v>362.3634698693878</v>
       </c>
       <c r="O55">
-        <v>114.6361334608163</v>
+        <v>108.7090409608163</v>
       </c>
       <c r="P55">
-        <v>267.4843114085715</v>
+        <v>253.6544289085714</v>
       </c>
       <c r="Q55">
-        <v>437.4843114085715</v>
+        <v>423.6544289085714</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1133884142196135</v>
+        <v>0.1146113860945484</v>
       </c>
       <c r="T55">
-        <v>1.560933353801698</v>
+        <v>1.589177507957237</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.265034630797123</v>
+        <v>2.125981109376776</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07695103760349224</v>
+        <v>0.07682842052376614</v>
       </c>
       <c r="C56">
-        <v>4589.280623090325</v>
+        <v>4518.643444040871</v>
       </c>
       <c r="D56">
-        <v>9329.376623090326</v>
+        <v>9351.713444040872</v>
       </c>
       <c r="E56">
-        <v>2576.696</v>
+        <v>2669.670000000001</v>
       </c>
       <c r="F56">
-        <v>5020.596</v>
+        <v>5113.570000000001</v>
       </c>
       <c r="G56">
         <v>280.5</v>
@@ -5885,28 +5885,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M56">
-        <v>321.8202036000001</v>
+        <v>327.779837</v>
       </c>
       <c r="N56">
-        <v>362.3634698693878</v>
+        <v>356.4038364693878</v>
       </c>
       <c r="O56">
-        <v>108.7090409608163</v>
+        <v>106.9211509408163</v>
       </c>
       <c r="P56">
-        <v>253.6544289085714</v>
+        <v>249.4826855285714</v>
       </c>
       <c r="Q56">
-        <v>423.6544289085714</v>
+        <v>419.4826855285714</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1146113860945484</v>
+        <v>0.1158887122750359</v>
       </c>
       <c r="T56">
-        <v>1.589177507957237</v>
+        <v>1.618676957853022</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.125981109376776</v>
+        <v>2.087326907388107</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07682842052376614</v>
+        <v>0.07670580344404003</v>
       </c>
       <c r="C57">
-        <v>4518.643444040871</v>
+        <v>4448.113481374021</v>
       </c>
       <c r="D57">
-        <v>9351.713444040872</v>
+        <v>9374.157481374021</v>
       </c>
       <c r="E57">
-        <v>2669.670000000001</v>
+        <v>2762.644</v>
       </c>
       <c r="F57">
-        <v>5113.570000000001</v>
+        <v>5206.544</v>
       </c>
       <c r="G57">
         <v>280.5</v>
@@ -5967,28 +5967,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M57">
-        <v>327.779837</v>
+        <v>333.7394704</v>
       </c>
       <c r="N57">
-        <v>356.4038364693878</v>
+        <v>350.4442030693878</v>
       </c>
       <c r="O57">
-        <v>106.9211509408163</v>
+        <v>105.1332609208163</v>
       </c>
       <c r="P57">
-        <v>249.4826855285714</v>
+        <v>245.3109421485715</v>
       </c>
       <c r="Q57">
-        <v>419.4826855285714</v>
+        <v>415.3109421485715</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1158887122750359</v>
+        <v>0.1172240987364546</v>
       </c>
       <c r="T57">
-        <v>1.618676957853022</v>
+        <v>1.64951729183498</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.087326907388107</v>
+        <v>2.050053212613319</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07670580344404003</v>
+        <v>0.07658318636431392</v>
       </c>
       <c r="C58">
-        <v>4448.113481374021</v>
+        <v>4377.6915089023</v>
       </c>
       <c r="D58">
-        <v>9374.157481374021</v>
+        <v>9396.709508902301</v>
       </c>
       <c r="E58">
-        <v>2762.644</v>
+        <v>2855.618</v>
       </c>
       <c r="F58">
-        <v>5206.544</v>
+        <v>5299.518</v>
       </c>
       <c r="G58">
         <v>280.5</v>
@@ -6049,28 +6049,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M58">
-        <v>333.7394704</v>
+        <v>339.6991038</v>
       </c>
       <c r="N58">
-        <v>350.4442030693878</v>
+        <v>344.4845696693878</v>
       </c>
       <c r="O58">
-        <v>105.1332609208163</v>
+        <v>103.3453709008163</v>
       </c>
       <c r="P58">
-        <v>245.3109421485715</v>
+        <v>241.1391987685714</v>
       </c>
       <c r="Q58">
-        <v>415.3109421485715</v>
+        <v>411.1391987685714</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1172240987364546</v>
+        <v>0.1186215961960789</v>
       </c>
       <c r="T58">
-        <v>1.64951729183498</v>
+        <v>1.681792059955633</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.050053212613319</v>
+        <v>2.014087366777998</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07658318636431392</v>
+        <v>0.07962736928458782</v>
       </c>
       <c r="C59">
-        <v>4377.6915089023</v>
+        <v>3755.10920096573</v>
       </c>
       <c r="D59">
-        <v>9396.709508902301</v>
+        <v>8867.10120096573</v>
       </c>
       <c r="E59">
-        <v>2855.618</v>
+        <v>2948.592</v>
       </c>
       <c r="F59">
-        <v>5299.518</v>
+        <v>5392.492</v>
       </c>
       <c r="G59">
         <v>280.5</v>
@@ -6131,45 +6131,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M59">
-        <v>339.6991038</v>
+        <v>387.7201748000001</v>
       </c>
       <c r="N59">
-        <v>344.4845696693878</v>
+        <v>296.4634986693878</v>
       </c>
       <c r="O59">
-        <v>103.3453709008163</v>
+        <v>88.93904960081633</v>
       </c>
       <c r="P59">
-        <v>241.1391987685714</v>
+        <v>207.5244490685714</v>
       </c>
       <c r="Q59">
-        <v>411.1391987685714</v>
+        <v>377.5244490685715</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1186215961960789</v>
+        <v>0.1200856411537805</v>
       </c>
       <c r="T59">
-        <v>1.681792059955633</v>
+        <v>1.715603721796317</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.014087366777998</v>
+        <v>1.764632634405249</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07962736928458782</v>
+        <v>0.0811700522048617</v>
       </c>
       <c r="C60">
-        <v>3755.10920096573</v>
+        <v>3415.907898709375</v>
       </c>
       <c r="D60">
-        <v>8867.10120096573</v>
+        <v>8620.873898709375</v>
       </c>
       <c r="E60">
-        <v>2948.591999999999</v>
+        <v>3041.565999999999</v>
       </c>
       <c r="F60">
-        <v>5392.491999999999</v>
+        <v>5485.465999999999</v>
       </c>
       <c r="G60">
         <v>280.5</v>
@@ -6213,45 +6213,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M60">
-        <v>387.7201748</v>
+        <v>415.7983228</v>
       </c>
       <c r="N60">
-        <v>296.4634986693878</v>
+        <v>268.3853506693878</v>
       </c>
       <c r="O60">
-        <v>88.93904960081635</v>
+        <v>80.51560520081635</v>
       </c>
       <c r="P60">
-        <v>207.5244490685715</v>
+        <v>187.8697454685715</v>
       </c>
       <c r="Q60">
-        <v>377.5244490685715</v>
+        <v>357.8697454685715</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1200856411537805</v>
+        <v>0.1216211029386871</v>
       </c>
       <c r="T60">
-        <v>1.715603721796317</v>
+        <v>1.751064732995083</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.764632634405249</v>
+        <v>1.645470017440358</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0811700522048617</v>
+        <v>0.08112933512513562</v>
       </c>
       <c r="C61">
-        <v>3415.907898709375</v>
+        <v>3329.256913586011</v>
       </c>
       <c r="D61">
-        <v>8620.873898709375</v>
+        <v>8627.196913586011</v>
       </c>
       <c r="E61">
-        <v>3041.565999999999</v>
+        <v>3134.54</v>
       </c>
       <c r="F61">
-        <v>5485.465999999999</v>
+        <v>5578.44</v>
       </c>
       <c r="G61">
         <v>280.5</v>
@@ -6295,28 +6295,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M61">
-        <v>415.7983228</v>
+        <v>422.845752</v>
       </c>
       <c r="N61">
-        <v>268.3853506693878</v>
+        <v>261.3379214693878</v>
       </c>
       <c r="O61">
-        <v>80.51560520081635</v>
+        <v>78.40137644081635</v>
       </c>
       <c r="P61">
-        <v>187.8697454685715</v>
+        <v>182.9365450285715</v>
       </c>
       <c r="Q61">
-        <v>357.8697454685715</v>
+        <v>352.9365450285715</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1216211029386871</v>
+        <v>0.123233337812839</v>
       </c>
       <c r="T61">
-        <v>1.751064732995083</v>
+        <v>1.788298794753788</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.645470017440358</v>
+        <v>1.618045517149686</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08112933512513562</v>
+        <v>0.08108861804540951</v>
       </c>
       <c r="C62">
-        <v>3329.256913586011</v>
+        <v>3242.615210552377</v>
       </c>
       <c r="D62">
-        <v>8627.196913586011</v>
+        <v>8633.529210552377</v>
       </c>
       <c r="E62">
-        <v>3134.54</v>
+        <v>3227.514</v>
       </c>
       <c r="F62">
-        <v>5578.44</v>
+        <v>5671.414</v>
       </c>
       <c r="G62">
         <v>280.5</v>
@@ -6377,28 +6377,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M62">
-        <v>422.845752</v>
+        <v>429.8931812</v>
       </c>
       <c r="N62">
-        <v>261.3379214693878</v>
+        <v>254.2904922693878</v>
       </c>
       <c r="O62">
-        <v>78.40137644081635</v>
+        <v>76.28714768081635</v>
       </c>
       <c r="P62">
-        <v>182.9365450285715</v>
+        <v>178.0033445885715</v>
       </c>
       <c r="Q62">
-        <v>352.9365450285715</v>
+        <v>348.0033445885715</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.123233337812839</v>
+        <v>0.1249282513984859</v>
       </c>
       <c r="T62">
-        <v>1.788298794753788</v>
+        <v>1.827442295577042</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.618045517149686</v>
+        <v>1.59152018080297</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08108861804540951</v>
+        <v>0.0810479009656834</v>
       </c>
       <c r="C63">
-        <v>3242.615210552377</v>
+        <v>3155.982810062434</v>
       </c>
       <c r="D63">
-        <v>8633.529210552377</v>
+        <v>8639.870810062434</v>
       </c>
       <c r="E63">
-        <v>3227.514</v>
+        <v>3320.488</v>
       </c>
       <c r="F63">
-        <v>5671.414</v>
+        <v>5764.388</v>
       </c>
       <c r="G63">
         <v>280.5</v>
@@ -6459,28 +6459,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M63">
-        <v>429.8931812</v>
+        <v>436.9406104</v>
       </c>
       <c r="N63">
-        <v>254.2904922693878</v>
+        <v>247.2430630693878</v>
       </c>
       <c r="O63">
-        <v>76.28714768081635</v>
+        <v>74.17291892081634</v>
       </c>
       <c r="P63">
-        <v>178.0033445885715</v>
+        <v>173.0701441485714</v>
       </c>
       <c r="Q63">
-        <v>348.0033445885715</v>
+        <v>343.0701441485714</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1249282513984859</v>
+        <v>0.1267123709623247</v>
       </c>
       <c r="T63">
-        <v>1.827442295577042</v>
+        <v>1.868645980654151</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.59152018080297</v>
+        <v>1.565850500467438</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0810479009656834</v>
+        <v>0.08100718388595729</v>
       </c>
       <c r="C64">
-        <v>3155.982810062434</v>
+        <v>3069.359732630283</v>
       </c>
       <c r="D64">
-        <v>8639.870810062434</v>
+        <v>8646.221732630283</v>
       </c>
       <c r="E64">
-        <v>3320.488</v>
+        <v>3413.462</v>
       </c>
       <c r="F64">
-        <v>5764.388</v>
+        <v>5857.362</v>
       </c>
       <c r="G64">
         <v>280.5</v>
@@ -6541,28 +6541,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M64">
-        <v>436.9406104</v>
+        <v>443.9880396</v>
       </c>
       <c r="N64">
-        <v>247.2430630693878</v>
+        <v>240.1956338693878</v>
       </c>
       <c r="O64">
-        <v>74.17291892081634</v>
+        <v>72.05869016081634</v>
       </c>
       <c r="P64">
-        <v>173.0701441485714</v>
+        <v>168.1369437085714</v>
       </c>
       <c r="Q64">
-        <v>343.0701441485714</v>
+        <v>338.1369437085714</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1267123709623247</v>
+        <v>0.1285929294215062</v>
       </c>
       <c r="T64">
-        <v>1.868645980654151</v>
+        <v>1.912076891951644</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.565850500467438</v>
+        <v>1.540995730618748</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08100718388595729</v>
+        <v>0.08096646680623119</v>
       </c>
       <c r="C65">
-        <v>3069.359732630283</v>
+        <v>2982.74599883039</v>
       </c>
       <c r="D65">
-        <v>8646.221732630283</v>
+        <v>8652.58199883039</v>
       </c>
       <c r="E65">
-        <v>3413.462</v>
+        <v>3506.436</v>
       </c>
       <c r="F65">
-        <v>5857.362</v>
+        <v>5950.336</v>
       </c>
       <c r="G65">
         <v>280.5</v>
@@ -6623,28 +6623,28 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M65">
-        <v>443.9880396</v>
+        <v>451.0354688</v>
       </c>
       <c r="N65">
-        <v>240.1956338693878</v>
+        <v>233.1482046693878</v>
       </c>
       <c r="O65">
-        <v>72.05869016081634</v>
+        <v>69.94446140081634</v>
       </c>
       <c r="P65">
-        <v>168.1369437085714</v>
+        <v>163.2037432685714</v>
       </c>
       <c r="Q65">
-        <v>338.1369437085714</v>
+        <v>333.2037432685714</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1285929294215062</v>
+        <v>0.1305779633506422</v>
       </c>
       <c r="T65">
-        <v>1.912076891951644</v>
+        <v>1.957920631654554</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.540995730618748</v>
+        <v>1.51691767232783</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08096646680623119</v>
+        <v>0.08738674972650508</v>
       </c>
       <c r="C66">
-        <v>2982.74599883039</v>
+        <v>1990.458166362063</v>
       </c>
       <c r="D66">
-        <v>8652.58199883039</v>
+        <v>7753.268166362063</v>
       </c>
       <c r="E66">
-        <v>3506.436</v>
+        <v>3599.41</v>
       </c>
       <c r="F66">
-        <v>5950.336</v>
+        <v>6043.31</v>
       </c>
       <c r="G66">
         <v>280.5</v>
@@ -6705,45 +6705,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M66">
-        <v>451.0354688</v>
+        <v>543.8979</v>
       </c>
       <c r="N66">
-        <v>233.1482046693878</v>
+        <v>140.2857734693878</v>
       </c>
       <c r="O66">
-        <v>69.94446140081634</v>
+        <v>42.08573204081633</v>
       </c>
       <c r="P66">
-        <v>163.2037432685714</v>
+        <v>98.20004142857144</v>
       </c>
       <c r="Q66">
-        <v>333.2037432685714</v>
+        <v>268.2000414285715</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1305779633506422</v>
+        <v>0.1326764277900145</v>
       </c>
       <c r="T66">
-        <v>1.957920631654554</v>
+        <v>2.006384013626201</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.51691767232783</v>
+        <v>1.257926668717397</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08738674972650508</v>
+        <v>0.1025126695273443</v>
       </c>
       <c r="C67">
-        <v>1990.458166362063</v>
+        <v>372.3977460785027</v>
       </c>
       <c r="D67">
-        <v>7753.268166362063</v>
+        <v>6228.181746078502</v>
       </c>
       <c r="E67">
-        <v>3599.41</v>
+        <v>3692.384</v>
       </c>
       <c r="F67">
-        <v>6043.31</v>
+        <v>6136.284</v>
       </c>
       <c r="G67">
         <v>280.5</v>
@@ -6787,45 +6787,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M67">
-        <v>543.8979</v>
+        <v>727.7632824</v>
       </c>
       <c r="N67">
-        <v>140.2857734693878</v>
+        <v>-43.57960893061215</v>
       </c>
       <c r="O67">
-        <v>42.08573204081633</v>
+        <v>-13.07388267918365</v>
       </c>
       <c r="P67">
-        <v>98.20004142857144</v>
+        <v>-30.50572625142851</v>
       </c>
       <c r="Q67">
-        <v>268.2000414285715</v>
+        <v>139.4942737485715</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1326764277900145</v>
+        <v>0.1362155369509842</v>
       </c>
       <c r="T67">
-        <v>2.006384013626201</v>
+        <v>2.088118636281389</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.3</v>
+        <v>0.2820355285910153</v>
       </c>
       <c r="W67">
-        <v>0.063</v>
+        <v>0.0851505863091056</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.257926668717397</v>
+        <v>0.9401184286367177</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1025126695273443</v>
+        <v>0.1032406695273443</v>
       </c>
       <c r="C68">
-        <v>372.3977460785027</v>
+        <v>221.013596098891</v>
       </c>
       <c r="D68">
-        <v>6228.181746078502</v>
+        <v>6169.771596098891</v>
       </c>
       <c r="E68">
-        <v>3692.384</v>
+        <v>3785.358</v>
       </c>
       <c r="F68">
-        <v>6136.284</v>
+        <v>6229.258</v>
       </c>
       <c r="G68">
         <v>280.5</v>
@@ -6869,37 +6869,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M68">
-        <v>727.7632824</v>
+        <v>738.7899988</v>
       </c>
       <c r="N68">
-        <v>-43.57960893061215</v>
+        <v>-54.60632533061221</v>
       </c>
       <c r="O68">
-        <v>-13.07388267918365</v>
+        <v>-16.38189759918366</v>
       </c>
       <c r="P68">
-        <v>-30.50572625142851</v>
+        <v>-38.22442773142855</v>
       </c>
       <c r="Q68">
-        <v>139.4942737485715</v>
+        <v>131.7755722685715</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1362155369509842</v>
+        <v>0.1389554017070746</v>
       </c>
       <c r="T68">
-        <v>2.088118636281389</v>
+        <v>2.151394958592947</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2820355285910153</v>
+        <v>0.2778260430896569</v>
       </c>
       <c r="W68">
-        <v>0.0851505863091056</v>
+        <v>0.0856498312895667</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9401184286367177</v>
+        <v>0.9260868102988562</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1032406695273443</v>
+        <v>0.1039686695273443</v>
       </c>
       <c r="C69">
-        <v>221.013596098891</v>
+        <v>70.71485000012672</v>
       </c>
       <c r="D69">
-        <v>6169.771596098891</v>
+        <v>6112.446850000127</v>
       </c>
       <c r="E69">
-        <v>3785.358</v>
+        <v>3878.332</v>
       </c>
       <c r="F69">
-        <v>6229.258</v>
+        <v>6322.232</v>
       </c>
       <c r="G69">
         <v>280.5</v>
@@ -6951,37 +6951,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M69">
-        <v>738.7899988</v>
+        <v>749.8167152000001</v>
       </c>
       <c r="N69">
-        <v>-54.60632533061221</v>
+        <v>-65.63304173061226</v>
       </c>
       <c r="O69">
-        <v>-16.38189759918366</v>
+        <v>-19.68991251918368</v>
       </c>
       <c r="P69">
-        <v>-38.22442773142855</v>
+        <v>-45.94312921142858</v>
       </c>
       <c r="Q69">
-        <v>131.7755722685715</v>
+        <v>124.0568707885714</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1389554017070746</v>
+        <v>0.1418665080104207</v>
       </c>
       <c r="T69">
-        <v>2.151394958592947</v>
+        <v>2.218626051048976</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2778260430896569</v>
+        <v>0.2737403659853972</v>
       </c>
       <c r="W69">
-        <v>0.0856498312895667</v>
+        <v>0.0861343925941319</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9260868102988562</v>
+        <v>0.9124678866179906</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1039686695273443</v>
+        <v>0.1046966695273443</v>
       </c>
       <c r="C70">
-        <v>70.71485000012672</v>
+        <v>-78.52846790716558</v>
       </c>
       <c r="D70">
-        <v>6112.446850000127</v>
+        <v>6056.177532092835</v>
       </c>
       <c r="E70">
-        <v>3878.332</v>
+        <v>3971.306</v>
       </c>
       <c r="F70">
-        <v>6322.232</v>
+        <v>6415.206</v>
       </c>
       <c r="G70">
         <v>280.5</v>
@@ -7033,37 +7033,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M70">
-        <v>749.8167152000001</v>
+        <v>760.8434316</v>
       </c>
       <c r="N70">
-        <v>-65.63304173061226</v>
+        <v>-76.6597581306122</v>
       </c>
       <c r="O70">
-        <v>-19.68991251918368</v>
+        <v>-22.99792743918366</v>
       </c>
       <c r="P70">
-        <v>-45.94312921142858</v>
+        <v>-53.66183069142855</v>
       </c>
       <c r="Q70">
-        <v>124.0568707885714</v>
+        <v>116.3381693085715</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1418665080104207</v>
+        <v>0.14496542762366</v>
       </c>
       <c r="T70">
-        <v>2.218626051048976</v>
+        <v>2.290194633340879</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2737403659853972</v>
+        <v>0.2697731143044494</v>
       </c>
       <c r="W70">
-        <v>0.0861343925941319</v>
+        <v>0.08660490864349231</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9124678866179906</v>
+        <v>0.8992437143481647</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1046966695273443</v>
+        <v>0.1054246695273443</v>
       </c>
       <c r="C71">
-        <v>-78.52846790716558</v>
+        <v>-226.7452395926612</v>
       </c>
       <c r="D71">
-        <v>6056.177532092835</v>
+        <v>6000.934760407339</v>
       </c>
       <c r="E71">
-        <v>3971.306</v>
+        <v>4064.28</v>
       </c>
       <c r="F71">
-        <v>6415.206</v>
+        <v>6508.18</v>
       </c>
       <c r="G71">
         <v>280.5</v>
@@ -7115,37 +7115,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M71">
-        <v>760.8434316</v>
+        <v>771.8701480000001</v>
       </c>
       <c r="N71">
-        <v>-76.6597581306122</v>
+        <v>-87.68647453061226</v>
       </c>
       <c r="O71">
-        <v>-22.99792743918366</v>
+        <v>-26.30594235918368</v>
       </c>
       <c r="P71">
-        <v>-53.66183069142855</v>
+        <v>-61.38053217142858</v>
       </c>
       <c r="Q71">
-        <v>116.3381693085715</v>
+        <v>108.6194678285714</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.14496542762366</v>
+        <v>0.1482709418777821</v>
       </c>
       <c r="T71">
-        <v>2.290194633340879</v>
+        <v>2.366534454452242</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2697731143044494</v>
+        <v>0.2659192126715287</v>
       </c>
       <c r="W71">
-        <v>0.08660490864349231</v>
+        <v>0.08706198137715672</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8992437143481647</v>
+        <v>0.8863973755717623</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1054246695273443</v>
+        <v>0.1061526695273443</v>
       </c>
       <c r="C72">
-        <v>-226.7452395926612</v>
+        <v>-373.9633027384698</v>
       </c>
       <c r="D72">
-        <v>6000.934760407339</v>
+        <v>5946.690697261531</v>
       </c>
       <c r="E72">
-        <v>4064.28</v>
+        <v>4157.254000000001</v>
       </c>
       <c r="F72">
-        <v>6508.18</v>
+        <v>6601.154</v>
       </c>
       <c r="G72">
         <v>280.5</v>
@@ -7197,37 +7197,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M72">
-        <v>771.8701480000001</v>
+        <v>782.8968644000001</v>
       </c>
       <c r="N72">
-        <v>-87.68647453061226</v>
+        <v>-98.71319093061231</v>
       </c>
       <c r="O72">
-        <v>-26.30594235918368</v>
+        <v>-29.61395727918369</v>
       </c>
       <c r="P72">
-        <v>-61.38053217142858</v>
+        <v>-69.09923365142862</v>
       </c>
       <c r="Q72">
-        <v>108.6194678285714</v>
+        <v>100.9007663485714</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1482709418777821</v>
+        <v>0.1518044226321884</v>
       </c>
       <c r="T72">
-        <v>2.366534454452242</v>
+        <v>2.448139090812665</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2659192126715287</v>
+        <v>0.262173871647986</v>
       </c>
       <c r="W72">
-        <v>0.08706198137715672</v>
+        <v>0.08750617882254887</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8863973755717623</v>
+        <v>0.8739129054932867</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1061526695273443</v>
+        <v>0.1068806695273443</v>
       </c>
       <c r="C73">
-        <v>-373.9633027384689</v>
+        <v>-520.2094975143063</v>
       </c>
       <c r="D73">
-        <v>5946.690697261531</v>
+        <v>5893.418502485693</v>
       </c>
       <c r="E73">
-        <v>4157.253999999999</v>
+        <v>4250.227999999999</v>
       </c>
       <c r="F73">
-        <v>6601.154</v>
+        <v>6694.128</v>
       </c>
       <c r="G73">
         <v>280.5</v>
@@ -7279,37 +7279,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M73">
-        <v>782.8968644</v>
+        <v>793.9235808000001</v>
       </c>
       <c r="N73">
-        <v>-98.7131909306122</v>
+        <v>-109.7399073306123</v>
       </c>
       <c r="O73">
-        <v>-29.61395727918366</v>
+        <v>-32.92197219918368</v>
       </c>
       <c r="P73">
-        <v>-69.09923365142853</v>
+        <v>-76.81793513142858</v>
       </c>
       <c r="Q73">
-        <v>100.9007663485715</v>
+        <v>93.18206486857142</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1518044226321883</v>
+        <v>0.1555902948690522</v>
       </c>
       <c r="T73">
-        <v>2.448139090812663</v>
+        <v>2.535572629770259</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2621738716479861</v>
+        <v>0.2585325678750973</v>
       </c>
       <c r="W73">
-        <v>0.08750617882254887</v>
+        <v>0.08793803745001345</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8739129054932868</v>
+        <v>0.8617752262503244</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1068806695273443</v>
+        <v>0.1076086695273443</v>
       </c>
       <c r="C74">
-        <v>-520.2094975143063</v>
+        <v>-665.5097108608261</v>
       </c>
       <c r="D74">
-        <v>5893.418502485693</v>
+        <v>5841.092289139174</v>
       </c>
       <c r="E74">
-        <v>4250.227999999999</v>
+        <v>4343.201999999999</v>
       </c>
       <c r="F74">
-        <v>6694.128</v>
+        <v>6787.102</v>
       </c>
       <c r="G74">
         <v>280.5</v>
@@ -7361,37 +7361,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M74">
-        <v>793.9235808000001</v>
+        <v>804.9502972</v>
       </c>
       <c r="N74">
-        <v>-109.7399073306123</v>
+        <v>-120.7666237306122</v>
       </c>
       <c r="O74">
-        <v>-32.92197219918368</v>
+        <v>-36.22998711918365</v>
       </c>
       <c r="P74">
-        <v>-76.81793513142858</v>
+        <v>-84.53663661142855</v>
       </c>
       <c r="Q74">
-        <v>93.18206486857142</v>
+        <v>85.46336338857145</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1555902948690522</v>
+        <v>0.1596566020864245</v>
       </c>
       <c r="T74">
-        <v>2.535572629770259</v>
+        <v>2.629482727169157</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2585325678750973</v>
+        <v>0.2549910258494111</v>
       </c>
       <c r="W74">
-        <v>0.08793803745001345</v>
+        <v>0.08835806433425986</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8617752262503244</v>
+        <v>0.8499700861647037</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1076086695273443</v>
+        <v>0.1083366695273443</v>
       </c>
       <c r="C75">
-        <v>-665.5097108608261</v>
+        <v>-809.888918434629</v>
       </c>
       <c r="D75">
-        <v>5841.092289139174</v>
+        <v>5789.687081565371</v>
       </c>
       <c r="E75">
-        <v>4343.201999999999</v>
+        <v>4436.175999999999</v>
       </c>
       <c r="F75">
-        <v>6787.102</v>
+        <v>6880.076</v>
       </c>
       <c r="G75">
         <v>280.5</v>
@@ -7443,37 +7443,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M75">
-        <v>804.9502972</v>
+        <v>815.9770136000001</v>
       </c>
       <c r="N75">
-        <v>-120.7666237306122</v>
+        <v>-131.7933401306123</v>
       </c>
       <c r="O75">
-        <v>-36.22998711918365</v>
+        <v>-39.53800203918367</v>
       </c>
       <c r="P75">
-        <v>-84.53663661142855</v>
+        <v>-92.25533809142857</v>
       </c>
       <c r="Q75">
-        <v>85.46336338857145</v>
+        <v>77.74466190857143</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1596566020864245</v>
+        <v>0.1640357021666716</v>
       </c>
       <c r="T75">
-        <v>2.629482727169157</v>
+        <v>2.730616678214125</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.2549910258494111</v>
+        <v>0.2515452011757704</v>
       </c>
       <c r="W75">
-        <v>0.08835806433425986</v>
+        <v>0.08876673914055364</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8499700861647037</v>
+        <v>0.8384840039192346</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1083366695273443</v>
+        <v>0.1090646695273443</v>
       </c>
       <c r="C76">
-        <v>-809.888918434629</v>
+        <v>-953.3712243577547</v>
       </c>
       <c r="D76">
-        <v>5789.687081565371</v>
+        <v>5739.178775642245</v>
       </c>
       <c r="E76">
-        <v>4436.175999999999</v>
+        <v>4529.15</v>
       </c>
       <c r="F76">
-        <v>6880.076</v>
+        <v>6973.049999999999</v>
       </c>
       <c r="G76">
         <v>280.5</v>
@@ -7525,37 +7525,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M76">
-        <v>815.9770136000001</v>
+        <v>827.00373</v>
       </c>
       <c r="N76">
-        <v>-131.7933401306123</v>
+        <v>-142.8200565306122</v>
       </c>
       <c r="O76">
-        <v>-39.53800203918367</v>
+        <v>-42.84601695918366</v>
       </c>
       <c r="P76">
-        <v>-92.25533809142857</v>
+        <v>-99.97403957142853</v>
       </c>
       <c r="Q76">
-        <v>77.74466190857143</v>
+        <v>70.02596042857147</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1640357021666716</v>
+        <v>0.1687651302533384</v>
       </c>
       <c r="T76">
-        <v>2.730616678214125</v>
+        <v>2.839841345342689</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.2515452011757704</v>
+        <v>0.2481912651600935</v>
       </c>
       <c r="W76">
-        <v>0.08876673914055364</v>
+        <v>0.08916451595201293</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8384840039192346</v>
+        <v>0.8273042172003116</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1090646695273443</v>
+        <v>0.1097926695273443</v>
       </c>
       <c r="C77">
-        <v>-953.3712243577547</v>
+        <v>-1095.979898904545</v>
       </c>
       <c r="D77">
-        <v>5739.178775642245</v>
+        <v>5689.544101095455</v>
       </c>
       <c r="E77">
-        <v>4529.15</v>
+        <v>4622.124</v>
       </c>
       <c r="F77">
-        <v>6973.049999999999</v>
+        <v>7066.023999999999</v>
       </c>
       <c r="G77">
         <v>280.5</v>
@@ -7607,37 +7607,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M77">
-        <v>827.00373</v>
+        <v>838.0304464</v>
       </c>
       <c r="N77">
-        <v>-142.8200565306122</v>
+        <v>-153.8467729306121</v>
       </c>
       <c r="O77">
-        <v>-42.84601695918366</v>
+        <v>-46.15403187918364</v>
       </c>
       <c r="P77">
-        <v>-99.97403957142853</v>
+        <v>-107.6927410514285</v>
       </c>
       <c r="Q77">
-        <v>70.02596042857147</v>
+        <v>62.3072589485715</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1687651302533384</v>
+        <v>0.1738886773472276</v>
       </c>
       <c r="T77">
-        <v>2.839841345342689</v>
+        <v>2.958168068065302</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.2481912651600935</v>
+        <v>0.2449255906185133</v>
       </c>
       <c r="W77">
-        <v>0.08916451595201293</v>
+        <v>0.08955182495264434</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8273042172003116</v>
+        <v>0.8164186353950443</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1097926695273443</v>
+        <v>0.1105206695273443</v>
       </c>
       <c r="C78">
-        <v>-1095.979898904545</v>
+        <v>-1237.737414249689</v>
       </c>
       <c r="D78">
-        <v>5689.544101095455</v>
+        <v>5640.76058575031</v>
       </c>
       <c r="E78">
-        <v>4622.124</v>
+        <v>4715.098</v>
       </c>
       <c r="F78">
-        <v>7066.023999999999</v>
+        <v>7158.998</v>
       </c>
       <c r="G78">
         <v>280.5</v>
@@ -7689,37 +7689,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M78">
-        <v>838.0304464</v>
+        <v>849.0571628</v>
       </c>
       <c r="N78">
-        <v>-153.8467729306121</v>
+        <v>-164.8734893306122</v>
       </c>
       <c r="O78">
-        <v>-46.15403187918364</v>
+        <v>-49.46204679918365</v>
       </c>
       <c r="P78">
-        <v>-107.6927410514285</v>
+        <v>-115.4114425314285</v>
       </c>
       <c r="Q78">
-        <v>62.3072589485715</v>
+        <v>54.58855746857147</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1738886773472276</v>
+        <v>0.1794577502753679</v>
       </c>
       <c r="T78">
-        <v>2.958168068065302</v>
+        <v>3.086784071024663</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.2449255906185133</v>
+        <v>0.2417447387922988</v>
       </c>
       <c r="W78">
-        <v>0.08955182495264434</v>
+        <v>0.08992907397923336</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8164186353950443</v>
+        <v>0.8058157959743295</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1105206695273443</v>
+        <v>0.1782429292772905</v>
       </c>
       <c r="C79">
-        <v>-1237.737414249689</v>
+        <v>-3833.565992507802</v>
       </c>
       <c r="D79">
-        <v>5640.76058575031</v>
+        <v>3137.906007492198</v>
       </c>
       <c r="E79">
-        <v>4715.098</v>
+        <v>4808.072</v>
       </c>
       <c r="F79">
-        <v>7158.998</v>
+        <v>7251.972</v>
       </c>
       <c r="G79">
         <v>280.5</v>
@@ -7771,45 +7771,45 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M79">
-        <v>849.0571628</v>
+        <v>1456.1959776</v>
       </c>
       <c r="N79">
-        <v>-164.8734893306122</v>
+        <v>-772.0123041306123</v>
       </c>
       <c r="O79">
-        <v>-49.46204679918365</v>
+        <v>-231.6036912391837</v>
       </c>
       <c r="P79">
-        <v>-115.4114425314285</v>
+        <v>-540.4086128914287</v>
       </c>
       <c r="Q79">
-        <v>54.58855746857147</v>
+        <v>-370.4086128914287</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1794577502753679</v>
+        <v>0.1986161014240037</v>
       </c>
       <c r="T79">
-        <v>3.086784071024663</v>
+        <v>3.529240217644427</v>
       </c>
       <c r="U79">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2417447387922988</v>
+        <v>0.1409529384767999</v>
       </c>
       <c r="W79">
-        <v>0.08992907397923336</v>
+        <v>0.1724966499538586</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8058157959743295</v>
+        <v>0.4698431282559998</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1782429292772905</v>
+        <v>0.1797929292772905</v>
       </c>
       <c r="C80">
-        <v>-3833.565992507802</v>
+        <v>-3958.086401951422</v>
       </c>
       <c r="D80">
-        <v>3137.906007492198</v>
+        <v>3106.359598048578</v>
       </c>
       <c r="E80">
-        <v>4808.072</v>
+        <v>4901.046</v>
       </c>
       <c r="F80">
-        <v>7251.972</v>
+        <v>7344.946</v>
       </c>
       <c r="G80">
         <v>280.5</v>
@@ -7853,37 +7853,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M80">
-        <v>1456.1959776</v>
+        <v>1474.8651568</v>
       </c>
       <c r="N80">
-        <v>-772.0123041306123</v>
+        <v>-790.6814833306122</v>
       </c>
       <c r="O80">
-        <v>-231.6036912391837</v>
+        <v>-237.2044449991836</v>
       </c>
       <c r="P80">
-        <v>-540.4086128914287</v>
+        <v>-553.4770383314285</v>
       </c>
       <c r="Q80">
-        <v>-370.4086128914287</v>
+        <v>-383.4770383314285</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1986161014240037</v>
+        <v>0.2058930586346706</v>
       </c>
       <c r="T80">
-        <v>3.529240217644427</v>
+        <v>3.697299275627496</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1409529384767999</v>
+        <v>0.1391687240657012</v>
       </c>
       <c r="W80">
-        <v>0.1724966499538586</v>
+        <v>0.1728549202076072</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4698431282559998</v>
+        <v>0.4638957468856707</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1797929292772905</v>
+        <v>0.1813429292772905</v>
       </c>
       <c r="C81">
-        <v>-3958.086401951422</v>
+        <v>-4081.978831657299</v>
       </c>
       <c r="D81">
-        <v>3106.359598048578</v>
+        <v>3075.441168342701</v>
       </c>
       <c r="E81">
-        <v>4901.046</v>
+        <v>4994.02</v>
       </c>
       <c r="F81">
-        <v>7344.946</v>
+        <v>7437.92</v>
       </c>
       <c r="G81">
         <v>280.5</v>
@@ -7935,37 +7935,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M81">
-        <v>1474.8651568</v>
+        <v>1493.534336</v>
       </c>
       <c r="N81">
-        <v>-790.6814833306122</v>
+        <v>-809.3506625306123</v>
       </c>
       <c r="O81">
-        <v>-237.2044449991836</v>
+        <v>-242.8051987591837</v>
       </c>
       <c r="P81">
-        <v>-553.4770383314285</v>
+        <v>-566.5454637714287</v>
       </c>
       <c r="Q81">
-        <v>-383.4770383314285</v>
+        <v>-396.5454637714287</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2058930586346706</v>
+        <v>0.2138977115664041</v>
       </c>
       <c r="T81">
-        <v>3.697299275627496</v>
+        <v>3.882164239408871</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1391687240657012</v>
+        <v>0.1374291150148799</v>
       </c>
       <c r="W81">
-        <v>0.1728549202076072</v>
+        <v>0.1732042337050121</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4638957468856707</v>
+        <v>0.4580970500495998</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1813429292772905</v>
+        <v>0.1828929292772905</v>
       </c>
       <c r="C82">
-        <v>-4081.978831657299</v>
+        <v>-4205.261848179507</v>
       </c>
       <c r="D82">
-        <v>3075.441168342701</v>
+        <v>3045.132151820493</v>
       </c>
       <c r="E82">
-        <v>4994.02</v>
+        <v>5086.994000000001</v>
       </c>
       <c r="F82">
-        <v>7437.92</v>
+        <v>7530.894</v>
       </c>
       <c r="G82">
         <v>280.5</v>
@@ -8017,37 +8017,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M82">
-        <v>1493.534336</v>
+        <v>1512.2035152</v>
       </c>
       <c r="N82">
-        <v>-809.3506625306123</v>
+        <v>-828.0198417306123</v>
       </c>
       <c r="O82">
-        <v>-242.8051987591837</v>
+        <v>-248.4059525191837</v>
       </c>
       <c r="P82">
-        <v>-566.5454637714287</v>
+        <v>-579.6138892114286</v>
       </c>
       <c r="Q82">
-        <v>-396.5454637714287</v>
+        <v>-409.6138892114286</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2138977115664041</v>
+        <v>0.2227449595435833</v>
       </c>
       <c r="T82">
-        <v>3.882164239408871</v>
+        <v>4.086488673061969</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1374291150148799</v>
+        <v>0.1357324592739555</v>
       </c>
       <c r="W82">
-        <v>0.1732042337050121</v>
+        <v>0.1735449221777897</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4580970500495998</v>
+        <v>0.452441530913185</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1828929292772905</v>
+        <v>0.1844429292772905</v>
       </c>
       <c r="C83">
-        <v>-4205.261848179507</v>
+        <v>-4327.953293308097</v>
       </c>
       <c r="D83">
-        <v>3045.132151820493</v>
+        <v>3015.414706691903</v>
       </c>
       <c r="E83">
-        <v>5086.994000000001</v>
+        <v>5179.968000000001</v>
       </c>
       <c r="F83">
-        <v>7530.894</v>
+        <v>7623.868</v>
       </c>
       <c r="G83">
         <v>280.5</v>
@@ -8099,37 +8099,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M83">
-        <v>1512.2035152</v>
+        <v>1530.8726944</v>
       </c>
       <c r="N83">
-        <v>-828.0198417306123</v>
+        <v>-846.6890209306124</v>
       </c>
       <c r="O83">
-        <v>-248.4059525191837</v>
+        <v>-254.0067062791837</v>
       </c>
       <c r="P83">
-        <v>-579.6138892114286</v>
+        <v>-592.6823146514287</v>
       </c>
       <c r="Q83">
-        <v>-409.6138892114286</v>
+        <v>-422.6823146514287</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2227449595435833</v>
+        <v>0.2325752350737824</v>
       </c>
       <c r="T83">
-        <v>4.086488673061969</v>
+        <v>4.313515821565413</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1357324592739555</v>
+        <v>0.1340771853803706</v>
       </c>
       <c r="W83">
-        <v>0.1735449221777897</v>
+        <v>0.1738773011756216</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.452441530913185</v>
+        <v>0.4469239512679022</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1844429292772905</v>
+        <v>0.1859929292772905</v>
       </c>
       <c r="C84">
-        <v>-4327.953293308097</v>
+        <v>-4450.070319092179</v>
       </c>
       <c r="D84">
-        <v>3015.414706691903</v>
+        <v>2986.271680907822</v>
       </c>
       <c r="E84">
-        <v>5179.968000000001</v>
+        <v>5272.942000000001</v>
       </c>
       <c r="F84">
-        <v>7623.868</v>
+        <v>7716.842000000001</v>
       </c>
       <c r="G84">
         <v>280.5</v>
@@ -8181,37 +8181,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M84">
-        <v>1530.8726944</v>
+        <v>1549.5418736</v>
       </c>
       <c r="N84">
-        <v>-846.6890209306124</v>
+        <v>-865.3582001306123</v>
       </c>
       <c r="O84">
-        <v>-254.0067062791837</v>
+        <v>-259.6074600391837</v>
       </c>
       <c r="P84">
-        <v>-592.6823146514287</v>
+        <v>-605.7507400914286</v>
       </c>
       <c r="Q84">
-        <v>-422.6823146514287</v>
+        <v>-435.7507400914286</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2325752350737824</v>
+        <v>0.2435620136075343</v>
       </c>
       <c r="T84">
-        <v>4.313515821565413</v>
+        <v>4.567252046363378</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1340771853803706</v>
+        <v>0.1324617976047035</v>
       </c>
       <c r="W84">
-        <v>0.1738773011756216</v>
+        <v>0.1742016710409755</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4469239512679022</v>
+        <v>0.4415393253490119</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1859929292772905</v>
+        <v>0.1875429292772905</v>
       </c>
       <c r="C85">
-        <v>-4450.070319092179</v>
+        <v>-4571.629420851507</v>
       </c>
       <c r="D85">
-        <v>2986.271680907822</v>
+        <v>2957.686579148493</v>
       </c>
       <c r="E85">
-        <v>5272.942000000001</v>
+        <v>5365.916000000001</v>
       </c>
       <c r="F85">
-        <v>7716.842000000001</v>
+        <v>7809.816000000001</v>
       </c>
       <c r="G85">
         <v>280.5</v>
@@ -8263,37 +8263,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M85">
-        <v>1549.5418736</v>
+        <v>1568.2110528</v>
       </c>
       <c r="N85">
-        <v>-865.3582001306123</v>
+        <v>-884.0273793306125</v>
       </c>
       <c r="O85">
-        <v>-259.6074600391837</v>
+        <v>-265.2082137991837</v>
       </c>
       <c r="P85">
-        <v>-605.7507400914286</v>
+        <v>-618.8191655314288</v>
       </c>
       <c r="Q85">
-        <v>-435.7507400914286</v>
+        <v>-448.8191655314288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2435620136075343</v>
+        <v>0.2559221394580052</v>
       </c>
       <c r="T85">
-        <v>4.567252046363378</v>
+        <v>4.85270529926109</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1324617976047035</v>
+        <v>0.1308848714427428</v>
       </c>
       <c r="W85">
-        <v>0.1742016710409755</v>
+        <v>0.1745183178142973</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4415393253490119</v>
+        <v>0.4362829048091426</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1875429292772905</v>
+        <v>0.1890929292772905</v>
       </c>
       <c r="C86">
-        <v>-4571.629420851506</v>
+        <v>-4692.646468310084</v>
       </c>
       <c r="D86">
-        <v>2957.686579148494</v>
+        <v>2929.643531689915</v>
       </c>
       <c r="E86">
-        <v>5365.915999999999</v>
+        <v>5458.889999999999</v>
       </c>
       <c r="F86">
-        <v>7809.816</v>
+        <v>7902.789999999999</v>
       </c>
       <c r="G86">
         <v>280.5</v>
@@ -8345,37 +8345,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M86">
-        <v>1568.2110528</v>
+        <v>1586.880232</v>
       </c>
       <c r="N86">
-        <v>-884.0273793306122</v>
+        <v>-902.6965585306119</v>
       </c>
       <c r="O86">
-        <v>-265.2082137991837</v>
+        <v>-270.8089675591835</v>
       </c>
       <c r="P86">
-        <v>-618.8191655314286</v>
+        <v>-631.8875909714284</v>
       </c>
       <c r="Q86">
-        <v>-448.8191655314286</v>
+        <v>-461.8875909714284</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.255922139458005</v>
+        <v>0.2699302820885387</v>
       </c>
       <c r="T86">
-        <v>4.852705299261086</v>
+        <v>5.176218985878492</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1308848714427428</v>
+        <v>0.1293450494257694</v>
       </c>
       <c r="W86">
-        <v>0.1745183178142972</v>
+        <v>0.1748275140753055</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4362829048091427</v>
+        <v>0.4311501647525646</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1890929292772905</v>
+        <v>0.1906429292772905</v>
       </c>
       <c r="C87">
-        <v>-4692.646468310084</v>
+        <v>-4813.136734975281</v>
       </c>
       <c r="D87">
-        <v>2929.643531689915</v>
+        <v>2902.127265024718</v>
       </c>
       <c r="E87">
-        <v>5458.889999999999</v>
+        <v>5551.864</v>
       </c>
       <c r="F87">
-        <v>7902.789999999999</v>
+        <v>7995.763999999999</v>
       </c>
       <c r="G87">
         <v>280.5</v>
@@ -8427,37 +8427,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M87">
-        <v>1586.880232</v>
+        <v>1605.5494112</v>
       </c>
       <c r="N87">
-        <v>-902.6965585306119</v>
+        <v>-921.3657377306121</v>
       </c>
       <c r="O87">
-        <v>-270.8089675591835</v>
+        <v>-276.4097213191836</v>
       </c>
       <c r="P87">
-        <v>-631.8875909714284</v>
+        <v>-644.9560164114284</v>
       </c>
       <c r="Q87">
-        <v>-461.8875909714284</v>
+        <v>-474.9560164114284</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2699302820885387</v>
+        <v>0.2859395879520058</v>
       </c>
       <c r="T87">
-        <v>5.176218985878492</v>
+        <v>5.545948913441243</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1293450494257694</v>
+        <v>0.1278410372231441</v>
       </c>
       <c r="W87">
-        <v>0.1748275140753055</v>
+        <v>0.1751295197255927</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4311501647525646</v>
+        <v>0.4261367907438138</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1906429292772905</v>
+        <v>0.1921929292772905</v>
       </c>
       <c r="C88">
-        <v>-4813.136734975281</v>
+        <v>-4933.114925876691</v>
       </c>
       <c r="D88">
-        <v>2902.127265024718</v>
+        <v>2875.123074123308</v>
       </c>
       <c r="E88">
-        <v>5551.864</v>
+        <v>5644.838</v>
       </c>
       <c r="F88">
-        <v>7995.763999999999</v>
+        <v>8088.737999999999</v>
       </c>
       <c r="G88">
         <v>280.5</v>
@@ -8509,37 +8509,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M88">
-        <v>1605.5494112</v>
+        <v>1624.2185904</v>
       </c>
       <c r="N88">
-        <v>-921.3657377306121</v>
+        <v>-940.034916930612</v>
       </c>
       <c r="O88">
-        <v>-276.4097213191836</v>
+        <v>-282.0104750791836</v>
       </c>
       <c r="P88">
-        <v>-644.9560164114284</v>
+        <v>-658.0244418514284</v>
       </c>
       <c r="Q88">
-        <v>-474.9560164114284</v>
+        <v>-488.0244418514284</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2859395879520058</v>
+        <v>0.3044118639483139</v>
       </c>
       <c r="T88">
-        <v>5.545948913441243</v>
+        <v>5.972560368321338</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1278410372231441</v>
+        <v>0.1263716000136827</v>
       </c>
       <c r="W88">
-        <v>0.1751295197255927</v>
+        <v>0.1754245827172525</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4261367907438138</v>
+        <v>0.4212386667122757</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1921929292772905</v>
+        <v>0.1937429292772905</v>
       </c>
       <c r="C89">
-        <v>-4933.114925876691</v>
+        <v>-5052.595203770637</v>
       </c>
       <c r="D89">
-        <v>2875.123074123308</v>
+        <v>2848.616796229362</v>
       </c>
       <c r="E89">
-        <v>5644.838</v>
+        <v>5737.812</v>
       </c>
       <c r="F89">
-        <v>8088.737999999999</v>
+        <v>8181.712</v>
       </c>
       <c r="G89">
         <v>280.5</v>
@@ -8591,37 +8591,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M89">
-        <v>1624.2185904</v>
+        <v>1642.8877696</v>
       </c>
       <c r="N89">
-        <v>-940.034916930612</v>
+        <v>-958.7040961306121</v>
       </c>
       <c r="O89">
-        <v>-282.0104750791836</v>
+        <v>-287.6112288391836</v>
       </c>
       <c r="P89">
-        <v>-658.0244418514284</v>
+        <v>-671.0928672914285</v>
       </c>
       <c r="Q89">
-        <v>-488.0244418514284</v>
+        <v>-501.0928672914285</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3044118639483139</v>
+        <v>0.3259628526106734</v>
       </c>
       <c r="T89">
-        <v>5.972560368321338</v>
+        <v>6.470273732348116</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1263716000136827</v>
+        <v>0.1249355591044363</v>
       </c>
       <c r="W89">
-        <v>0.1754245827172525</v>
+        <v>0.1757129397318292</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4212386667122757</v>
+        <v>0.4164518636814544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1937429292772905</v>
+        <v>0.1952929292772905</v>
       </c>
       <c r="C90">
-        <v>-5052.595203770637</v>
+        <v>-5171.591213908399</v>
       </c>
       <c r="D90">
-        <v>2848.616796229362</v>
+        <v>2822.5947860916</v>
       </c>
       <c r="E90">
-        <v>5737.812</v>
+        <v>5830.786</v>
       </c>
       <c r="F90">
-        <v>8181.712</v>
+        <v>8274.686</v>
       </c>
       <c r="G90">
         <v>280.5</v>
@@ -8673,37 +8673,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M90">
-        <v>1642.8877696</v>
+        <v>1661.5569488</v>
       </c>
       <c r="N90">
-        <v>-958.7040961306121</v>
+        <v>-977.3732753306123</v>
       </c>
       <c r="O90">
-        <v>-287.6112288391836</v>
+        <v>-293.2119825991837</v>
       </c>
       <c r="P90">
-        <v>-671.0928672914285</v>
+        <v>-684.1612927314286</v>
       </c>
       <c r="Q90">
-        <v>-501.0928672914285</v>
+        <v>-514.1612927314286</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3259628526106734</v>
+        <v>0.3514322028480075</v>
       </c>
       <c r="T90">
-        <v>6.470273732348116</v>
+        <v>7.058480435288856</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1249355591044363</v>
+        <v>0.1235317887774202</v>
       </c>
       <c r="W90">
-        <v>0.1757129397318292</v>
+        <v>0.175994816813494</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4164518636814544</v>
+        <v>0.4117726292580672</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1952929292772905</v>
+        <v>0.1968429292772905</v>
       </c>
       <c r="C91">
-        <v>-5171.591213908399</v>
+        <v>-5290.116107459195</v>
       </c>
       <c r="D91">
-        <v>2822.5947860916</v>
+        <v>2797.043892540806</v>
       </c>
       <c r="E91">
-        <v>5830.786</v>
+        <v>5923.76</v>
       </c>
       <c r="F91">
-        <v>8274.686</v>
+        <v>8367.66</v>
       </c>
       <c r="G91">
         <v>280.5</v>
@@ -8755,37 +8755,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M91">
-        <v>1661.5569488</v>
+        <v>1680.226128</v>
       </c>
       <c r="N91">
-        <v>-977.3732753306123</v>
+        <v>-996.0424545306122</v>
       </c>
       <c r="O91">
-        <v>-293.2119825991837</v>
+        <v>-298.8127363591836</v>
       </c>
       <c r="P91">
-        <v>-684.1612927314286</v>
+        <v>-697.2297181714285</v>
       </c>
       <c r="Q91">
-        <v>-514.1612927314286</v>
+        <v>-527.2297181714285</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3514322028480075</v>
+        <v>0.3819954231328082</v>
       </c>
       <c r="T91">
-        <v>7.058480435288856</v>
+        <v>7.764328478817742</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1235317887774202</v>
+        <v>0.1221592133465599</v>
       </c>
       <c r="W91">
-        <v>0.175994816813494</v>
+        <v>0.1762704299600108</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4117726292580672</v>
+        <v>0.4071973778218665</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1968429292772905</v>
+        <v>0.1983929292772905</v>
       </c>
       <c r="C92">
-        <v>-5290.116107459195</v>
+        <v>-5408.182563672382</v>
       </c>
       <c r="D92">
-        <v>2797.043892540806</v>
+        <v>2771.951436327618</v>
       </c>
       <c r="E92">
-        <v>5923.76</v>
+        <v>6016.734</v>
       </c>
       <c r="F92">
-        <v>8367.66</v>
+        <v>8460.634</v>
       </c>
       <c r="G92">
         <v>280.5</v>
@@ -8837,37 +8837,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M92">
-        <v>1680.226128</v>
+        <v>1698.8953072</v>
       </c>
       <c r="N92">
-        <v>-996.0424545306122</v>
+        <v>-1014.711633730612</v>
       </c>
       <c r="O92">
-        <v>-298.8127363591836</v>
+        <v>-304.4134901191837</v>
       </c>
       <c r="P92">
-        <v>-697.2297181714285</v>
+        <v>-710.2981436114287</v>
       </c>
       <c r="Q92">
-        <v>-527.2297181714285</v>
+        <v>-540.2981436114287</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3819954231328082</v>
+        <v>0.4193504701475647</v>
       </c>
       <c r="T92">
-        <v>7.764328478817742</v>
+        <v>8.627031643130824</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1221592133465599</v>
+        <v>0.1208168044086856</v>
       </c>
       <c r="W92">
-        <v>0.1762704299600108</v>
+        <v>0.1765399856747359</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4071973778218665</v>
+        <v>0.4027226813622855</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1983929292772905</v>
+        <v>0.1999429292772905</v>
       </c>
       <c r="C93">
-        <v>-5408.182563672382</v>
+        <v>-5525.802810857372</v>
       </c>
       <c r="D93">
-        <v>2771.951436327618</v>
+        <v>2747.305189142628</v>
       </c>
       <c r="E93">
-        <v>6016.734</v>
+        <v>6109.708000000001</v>
       </c>
       <c r="F93">
-        <v>8460.634</v>
+        <v>8553.608</v>
       </c>
       <c r="G93">
         <v>280.5</v>
@@ -8919,37 +8919,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M93">
-        <v>1698.8953072</v>
+        <v>1717.5644864</v>
       </c>
       <c r="N93">
-        <v>-1014.711633730612</v>
+        <v>-1033.380812930612</v>
       </c>
       <c r="O93">
-        <v>-304.4134901191837</v>
+        <v>-310.0142438791837</v>
       </c>
       <c r="P93">
-        <v>-710.2981436114287</v>
+        <v>-723.3665690514285</v>
       </c>
       <c r="Q93">
-        <v>-540.2981436114287</v>
+        <v>-553.3665690514285</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4193504701475647</v>
+        <v>0.4660442789160104</v>
       </c>
       <c r="T93">
-        <v>8.627031643130824</v>
+        <v>9.70541059852218</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1208168044086856</v>
+        <v>0.1195035782738086</v>
       </c>
       <c r="W93">
-        <v>0.1765399856747359</v>
+        <v>0.1768036814826192</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4027226813622855</v>
+        <v>0.3983452609126955</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1999429292772905</v>
+        <v>0.2014929292772905</v>
       </c>
       <c r="C94">
-        <v>-5525.802810857372</v>
+        <v>-5642.988646254148</v>
       </c>
       <c r="D94">
-        <v>2747.305189142628</v>
+        <v>2723.093353745852</v>
       </c>
       <c r="E94">
-        <v>6109.708000000001</v>
+        <v>6202.682000000001</v>
       </c>
       <c r="F94">
-        <v>8553.608</v>
+        <v>8646.582</v>
       </c>
       <c r="G94">
         <v>280.5</v>
@@ -9001,37 +9001,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M94">
-        <v>1717.5644864</v>
+        <v>1736.2336656</v>
       </c>
       <c r="N94">
-        <v>-1033.380812930612</v>
+        <v>-1052.049992130612</v>
       </c>
       <c r="O94">
-        <v>-310.0142438791837</v>
+        <v>-315.6149976391837</v>
       </c>
       <c r="P94">
-        <v>-723.3665690514285</v>
+        <v>-736.4349944914286</v>
       </c>
       <c r="Q94">
-        <v>-553.3665690514285</v>
+        <v>-566.4349944914286</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4660442789160104</v>
+        <v>0.5260791759040119</v>
       </c>
       <c r="T94">
-        <v>9.70541059852218</v>
+        <v>11.09189782688249</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1195035782738086</v>
+        <v>0.118218593561187</v>
       </c>
       <c r="W94">
-        <v>0.1768036814826192</v>
+        <v>0.1770617064129137</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3983452609126955</v>
+        <v>0.3940619785372902</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2014929292772905</v>
+        <v>0.2030429292772905</v>
       </c>
       <c r="C95">
-        <v>-5642.988646254148</v>
+        <v>-5759.751454862282</v>
       </c>
       <c r="D95">
-        <v>2723.093353745852</v>
+        <v>2699.304545137719</v>
       </c>
       <c r="E95">
-        <v>6202.682000000001</v>
+        <v>6295.656000000001</v>
       </c>
       <c r="F95">
-        <v>8646.582</v>
+        <v>8739.556</v>
       </c>
       <c r="G95">
         <v>280.5</v>
@@ -9083,37 +9083,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M95">
-        <v>1736.2336656</v>
+        <v>1754.9028448</v>
       </c>
       <c r="N95">
-        <v>-1052.049992130612</v>
+        <v>-1070.719171330612</v>
       </c>
       <c r="O95">
-        <v>-315.6149976391837</v>
+        <v>-321.2157513991837</v>
       </c>
       <c r="P95">
-        <v>-736.4349944914286</v>
+        <v>-749.5034199314287</v>
       </c>
       <c r="Q95">
-        <v>-566.4349944914286</v>
+        <v>-579.5034199314287</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5260791759040119</v>
+        <v>0.6061257052213472</v>
       </c>
       <c r="T95">
-        <v>11.09189782688249</v>
+        <v>12.94054746469624</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.118218593561187</v>
+        <v>0.116960948948834</v>
       </c>
       <c r="W95">
-        <v>0.1770617064129137</v>
+        <v>0.1773142414510741</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3940619785372902</v>
+        <v>0.3898698298294465</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2030429292772905</v>
+        <v>0.2045929292772905</v>
       </c>
       <c r="C96">
-        <v>-5759.751454862282</v>
+        <v>-5876.102227291543</v>
       </c>
       <c r="D96">
-        <v>2699.304545137719</v>
+        <v>2675.927772708457</v>
       </c>
       <c r="E96">
-        <v>6295.656000000001</v>
+        <v>6388.630000000001</v>
       </c>
       <c r="F96">
-        <v>8739.556</v>
+        <v>8832.530000000001</v>
       </c>
       <c r="G96">
         <v>280.5</v>
@@ -9165,37 +9165,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M96">
-        <v>1754.9028448</v>
+        <v>1773.572024</v>
       </c>
       <c r="N96">
-        <v>-1070.719171330612</v>
+        <v>-1089.388350530613</v>
       </c>
       <c r="O96">
-        <v>-321.2157513991837</v>
+        <v>-326.8165051591837</v>
       </c>
       <c r="P96">
-        <v>-749.5034199314287</v>
+        <v>-762.5718453714288</v>
       </c>
       <c r="Q96">
-        <v>-579.5034199314287</v>
+        <v>-592.5718453714288</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6061257052213472</v>
+        <v>0.7181908462656171</v>
       </c>
       <c r="T96">
-        <v>12.94054746469624</v>
+        <v>15.5286569576355</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.116960948948834</v>
+        <v>0.115729781065162</v>
       </c>
       <c r="W96">
-        <v>0.1773142414510741</v>
+        <v>0.1775614599621154</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3898698298294465</v>
+        <v>0.3857659368838734</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2045929292772905</v>
+        <v>0.2061429292772905</v>
       </c>
       <c r="C97">
-        <v>-5876.102227291543</v>
+        <v>-5992.051576692935</v>
       </c>
       <c r="D97">
-        <v>2675.927772708457</v>
+        <v>2652.952423307066</v>
       </c>
       <c r="E97">
-        <v>6388.630000000001</v>
+        <v>6481.604000000001</v>
       </c>
       <c r="F97">
-        <v>8832.530000000001</v>
+        <v>8925.504000000001</v>
       </c>
       <c r="G97">
         <v>280.5</v>
@@ -9247,37 +9247,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M97">
-        <v>1773.572024</v>
+        <v>1792.2412032</v>
       </c>
       <c r="N97">
-        <v>-1089.388350530613</v>
+        <v>-1108.057529730612</v>
       </c>
       <c r="O97">
-        <v>-326.8165051591837</v>
+        <v>-332.4172589191837</v>
       </c>
       <c r="P97">
-        <v>-762.5718453714288</v>
+        <v>-775.6402708114285</v>
       </c>
       <c r="Q97">
-        <v>-592.5718453714288</v>
+        <v>-605.6402708114285</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7181908462656171</v>
+        <v>0.8862885578320218</v>
       </c>
       <c r="T97">
-        <v>15.5286569576355</v>
+        <v>19.41082119704438</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.115729781065162</v>
+        <v>0.1145242625123999</v>
       </c>
       <c r="W97">
-        <v>0.1775614599621154</v>
+        <v>0.1778035280875101</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3857659368838734</v>
+        <v>0.3817475417079998</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2061429292772905</v>
+        <v>0.2076929292772905</v>
       </c>
       <c r="C98">
-        <v>-5992.051576692933</v>
+        <v>-6107.609754824938</v>
       </c>
       <c r="D98">
-        <v>2652.952423307066</v>
+        <v>2630.368245175061</v>
       </c>
       <c r="E98">
-        <v>6481.603999999999</v>
+        <v>6574.578</v>
       </c>
       <c r="F98">
-        <v>8925.503999999999</v>
+        <v>9018.477999999999</v>
       </c>
       <c r="G98">
         <v>280.5</v>
@@ -9329,37 +9329,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M98">
-        <v>1792.2412032</v>
+        <v>1810.9103824</v>
       </c>
       <c r="N98">
-        <v>-1108.057529730612</v>
+        <v>-1126.726708930612</v>
       </c>
       <c r="O98">
-        <v>-332.4172589191836</v>
+        <v>-338.0180126791836</v>
       </c>
       <c r="P98">
-        <v>-775.6402708114283</v>
+        <v>-788.7086962514284</v>
       </c>
       <c r="Q98">
-        <v>-605.6402708114283</v>
+        <v>-618.7086962514284</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8862885578320193</v>
+        <v>1.166451410442693</v>
       </c>
       <c r="T98">
-        <v>19.41082119704433</v>
+        <v>25.88109492939245</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1145242625124</v>
+        <v>0.1133436000122721</v>
       </c>
       <c r="W98">
-        <v>0.1778035280875101</v>
+        <v>0.1780406051175358</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.381747541708</v>
+        <v>0.3778120000409072</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2076929292772905</v>
+        <v>0.2092429292772905</v>
       </c>
       <c r="C99">
-        <v>-6107.609754824938</v>
+        <v>-6222.786667306063</v>
       </c>
       <c r="D99">
-        <v>2630.368245175061</v>
+        <v>2608.165332693936</v>
       </c>
       <c r="E99">
-        <v>6574.578</v>
+        <v>6667.552</v>
       </c>
       <c r="F99">
-        <v>9018.477999999999</v>
+        <v>9111.451999999999</v>
       </c>
       <c r="G99">
         <v>280.5</v>
@@ -9411,37 +9411,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M99">
-        <v>1810.9103824</v>
+        <v>1829.5795616</v>
       </c>
       <c r="N99">
-        <v>-1126.726708930612</v>
+        <v>-1145.395888130612</v>
       </c>
       <c r="O99">
-        <v>-338.0180126791836</v>
+        <v>-343.6187664391836</v>
       </c>
       <c r="P99">
-        <v>-788.7086962514284</v>
+        <v>-801.7771216914284</v>
       </c>
       <c r="Q99">
-        <v>-618.7086962514284</v>
+        <v>-631.7771216914284</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.166451410442693</v>
+        <v>1.726777115664039</v>
       </c>
       <c r="T99">
-        <v>25.88109492939245</v>
+        <v>38.82164239408866</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1133436000122721</v>
+        <v>0.1121870326652081</v>
       </c>
       <c r="W99">
-        <v>0.1780406051175358</v>
+        <v>0.1782728438408262</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3778120000409072</v>
+        <v>0.3739567755506937</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2092429292772905</v>
+        <v>0.2107929292772905</v>
       </c>
       <c r="C100">
-        <v>-6222.786667306063</v>
+        <v>-6337.59188810139</v>
       </c>
       <c r="D100">
-        <v>2608.165332693936</v>
+        <v>2586.334111898609</v>
       </c>
       <c r="E100">
-        <v>6667.552</v>
+        <v>6760.526</v>
       </c>
       <c r="F100">
-        <v>9111.451999999999</v>
+        <v>9204.425999999999</v>
       </c>
       <c r="G100">
         <v>280.5</v>
@@ -9493,37 +9493,37 @@
         <v>684.1836734693878</v>
       </c>
       <c r="M100">
-        <v>1829.5795616</v>
+        <v>1848.2487408</v>
       </c>
       <c r="N100">
-        <v>-1145.395888130612</v>
+        <v>-1164.065067330612</v>
       </c>
       <c r="O100">
-        <v>-343.6187664391836</v>
+        <v>-349.2195201991836</v>
       </c>
       <c r="P100">
-        <v>-801.7771216914284</v>
+        <v>-814.8455471314286</v>
       </c>
       <c r="Q100">
-        <v>-631.7771216914284</v>
+        <v>-644.8455471314286</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.726777115664039</v>
+        <v>3.407754231328077</v>
       </c>
       <c r="T100">
-        <v>38.82164239408866</v>
+        <v>77.64328478817731</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1121870326652081</v>
+        <v>0.1110538303150545</v>
       </c>
       <c r="W100">
-        <v>0.1782728438408262</v>
+        <v>0.1785003908727371</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3739567755506937</v>
+        <v>0.370179434383515</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2107929292772905</v>
-      </c>
-      <c r="C101">
-        <v>-6337.59188810139</v>
-      </c>
-      <c r="D101">
-        <v>2586.334111898609</v>
-      </c>
-      <c r="E101">
-        <v>6760.526</v>
-      </c>
-      <c r="F101">
-        <v>9204.425999999999</v>
-      </c>
-      <c r="G101">
-        <v>280.5</v>
-      </c>
-      <c r="H101">
-        <v>6853.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>854.1836734693878</v>
-      </c>
-      <c r="K101">
-        <v>170</v>
-      </c>
-      <c r="L101">
-        <v>684.1836734693878</v>
-      </c>
-      <c r="M101">
-        <v>1848.2487408</v>
-      </c>
-      <c r="N101">
-        <v>-1164.065067330612</v>
-      </c>
-      <c r="O101">
-        <v>-349.2195201991836</v>
-      </c>
-      <c r="P101">
-        <v>-814.8455471314286</v>
-      </c>
-      <c r="Q101">
-        <v>-644.8455471314286</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.407754231328077</v>
-      </c>
-      <c r="T101">
-        <v>77.64328478817731</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1110538303150545</v>
-      </c>
-      <c r="W101">
-        <v>0.1785003908727371</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.370179434383515</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
